--- a/csv_excel_diff.xlsx
+++ b/csv_excel_diff.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="仅CSV有" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="仅Excel有" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="paid为0" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="closed为0_未关闭" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="close_date为空" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="hide为1_隐藏" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="含非微信非支付宝" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="应通过但CSV没有" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅CSV有" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="仅Excel有" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="paid为0" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="closed为0_未关闭" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="close_date为空" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="hide为1_隐藏" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="含非微信非支付宝" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="应通过但CSV没有" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -37138,8 +37138,6 @@
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -37190,8 +37188,6 @@
       <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>0</v>
       </c>
@@ -37232,8 +37228,6 @@
       <c r="K4" t="n">
         <v>1</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>0</v>
       </c>
@@ -37274,8 +37268,6 @@
       <c r="K5" t="n">
         <v>1</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -37326,8 +37318,6 @@
       <c r="K6" t="n">
         <v>1</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -37378,8 +37368,6 @@
       <c r="K7" t="n">
         <v>1</v>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -37430,8 +37418,6 @@
       <c r="K8" t="n">
         <v>1</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -37482,8 +37468,6 @@
       <c r="K9" t="n">
         <v>1</v>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -37524,8 +37508,6 @@
       <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -37566,8 +37548,6 @@
       <c r="K11" t="n">
         <v>1</v>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -37608,8 +37588,6 @@
       <c r="K12" t="n">
         <v>1</v>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -37660,8 +37638,6 @@
       <c r="K13" t="n">
         <v>1</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -37712,8 +37688,6 @@
       <c r="K14" t="n">
         <v>1</v>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -37764,8 +37738,6 @@
       <c r="K15" t="n">
         <v>1</v>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -37816,8 +37788,6 @@
       <c r="K16" t="n">
         <v>1</v>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -37868,8 +37838,6 @@
       <c r="K17" t="n">
         <v>1</v>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -37920,8 +37888,6 @@
       <c r="K18" t="n">
         <v>1</v>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -37972,8 +37938,6 @@
       <c r="K19" t="n">
         <v>1</v>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -38024,8 +37988,6 @@
       <c r="K20" t="n">
         <v>1</v>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -38076,8 +38038,6 @@
       <c r="K21" t="n">
         <v>1</v>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -38128,8 +38088,6 @@
       <c r="K22" t="n">
         <v>1</v>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -38180,8 +38138,6 @@
       <c r="K23" t="n">
         <v>1</v>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -38232,8 +38188,6 @@
       <c r="K24" t="n">
         <v>1</v>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -38284,8 +38238,6 @@
       <c r="K25" t="n">
         <v>1</v>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -38336,8 +38288,6 @@
       <c r="K26" t="n">
         <v>1</v>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -38378,8 +38328,6 @@
       <c r="K27" t="n">
         <v>1</v>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -38430,8 +38378,6 @@
       <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -38482,8 +38428,6 @@
       <c r="K29" t="n">
         <v>1</v>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
         <v>0</v>
       </c>
@@ -38534,8 +38478,6 @@
       <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>0</v>
       </c>
@@ -38586,8 +38528,6 @@
       <c r="K31" t="n">
         <v>1</v>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
         <v>0</v>
       </c>
@@ -38638,8 +38578,6 @@
       <c r="K32" t="n">
         <v>1</v>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>0</v>
       </c>
@@ -38680,8 +38618,6 @@
       <c r="K33" t="n">
         <v>1</v>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
         <v>0</v>
       </c>
@@ -38722,8 +38658,6 @@
       <c r="K34" t="n">
         <v>1</v>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>0</v>
       </c>
@@ -38774,8 +38708,6 @@
       <c r="K35" t="n">
         <v>1</v>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -38816,8 +38748,6 @@
       <c r="K36" t="n">
         <v>1</v>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -38868,8 +38798,6 @@
       <c r="K37" t="n">
         <v>1</v>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>0</v>
       </c>
@@ -38920,8 +38848,6 @@
       <c r="K38" t="n">
         <v>1</v>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>0</v>
       </c>
@@ -38972,8 +38898,6 @@
       <c r="K39" t="n">
         <v>1</v>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>0</v>
       </c>
@@ -39024,8 +38948,6 @@
       <c r="K40" t="n">
         <v>1</v>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>0</v>
       </c>
@@ -39076,8 +38998,6 @@
       <c r="K41" t="n">
         <v>1</v>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
         <v>0</v>
       </c>
@@ -39118,8 +39038,6 @@
       <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
         <v>0</v>
       </c>
@@ -39160,8 +39078,6 @@
       <c r="K43" t="n">
         <v>1</v>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>0</v>
       </c>
@@ -39212,8 +39128,6 @@
       <c r="K44" t="n">
         <v>1</v>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>0</v>
       </c>
@@ -39264,8 +39178,6 @@
       <c r="K45" t="n">
         <v>1</v>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
         <v>0</v>
       </c>
@@ -39316,8 +39228,6 @@
       <c r="K46" t="n">
         <v>1</v>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>0</v>
       </c>
@@ -39368,8 +39278,6 @@
       <c r="K47" t="n">
         <v>1</v>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
         <v>0</v>
       </c>
@@ -39410,8 +39318,6 @@
       <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
         <v>0</v>
       </c>
@@ -39452,8 +39358,6 @@
       <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -39504,8 +39408,6 @@
       <c r="K50" t="n">
         <v>1</v>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
         <v>0</v>
       </c>
@@ -39546,8 +39448,6 @@
       <c r="K51" t="n">
         <v>1</v>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -39588,8 +39488,6 @@
       <c r="K52" t="n">
         <v>1</v>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
         <v>0</v>
       </c>
@@ -39630,8 +39528,6 @@
       <c r="K53" t="n">
         <v>1</v>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
         <v>0</v>
       </c>
@@ -39672,8 +39568,6 @@
       <c r="K54" t="n">
         <v>1</v>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
         <v>0</v>
       </c>
@@ -39714,8 +39608,6 @@
       <c r="K55" t="n">
         <v>1</v>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>0</v>
       </c>
@@ -39766,8 +39658,6 @@
       <c r="K56" t="n">
         <v>1</v>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
         <v>0</v>
       </c>
@@ -39818,8 +39708,6 @@
       <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
         <v>0</v>
       </c>
@@ -39870,8 +39758,6 @@
       <c r="K58" t="n">
         <v>1</v>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
         <v>0</v>
       </c>
@@ -39922,8 +39808,6 @@
       <c r="K59" t="n">
         <v>1</v>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
         <v>0</v>
       </c>
@@ -39974,8 +39858,6 @@
       <c r="K60" t="n">
         <v>1</v>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
         <v>0</v>
       </c>
@@ -40026,8 +39908,6 @@
       <c r="K61" t="n">
         <v>1</v>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
         <v>0</v>
       </c>
@@ -40078,8 +39958,6 @@
       <c r="K62" t="n">
         <v>1</v>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
         <v>0</v>
       </c>
@@ -40130,8 +40008,6 @@
       <c r="K63" t="n">
         <v>1</v>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
         <v>0</v>
       </c>
@@ -40182,8 +40058,6 @@
       <c r="K64" t="n">
         <v>1</v>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
         <v>0</v>
       </c>
@@ -40234,8 +40108,6 @@
       <c r="K65" t="n">
         <v>1</v>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
         <v>0</v>
       </c>
@@ -40286,8 +40158,6 @@
       <c r="K66" t="n">
         <v>1</v>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
         <v>0</v>
       </c>
@@ -40338,8 +40208,6 @@
       <c r="K67" t="n">
         <v>1</v>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
         <v>0</v>
       </c>
@@ -40390,8 +40258,6 @@
       <c r="K68" t="n">
         <v>1</v>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
         <v>0</v>
       </c>
@@ -40442,8 +40308,6 @@
       <c r="K69" t="n">
         <v>1</v>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
         <v>0</v>
       </c>
@@ -40494,8 +40358,6 @@
       <c r="K70" t="n">
         <v>1</v>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
         <v>0</v>
       </c>
@@ -40546,8 +40408,6 @@
       <c r="K71" t="n">
         <v>1</v>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
         <v>0</v>
       </c>
@@ -40588,8 +40448,6 @@
       <c r="K72" t="n">
         <v>1</v>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
         <v>0</v>
       </c>
@@ -40640,8 +40498,6 @@
       <c r="K73" t="n">
         <v>1</v>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
         <v>0</v>
       </c>
@@ -40692,8 +40548,6 @@
       <c r="K74" t="n">
         <v>1</v>
       </c>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
         <v>0</v>
       </c>
@@ -40744,8 +40598,6 @@
       <c r="K75" t="n">
         <v>1</v>
       </c>
-      <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
         <v>0</v>
       </c>
@@ -40786,8 +40638,6 @@
       <c r="K76" t="n">
         <v>1</v>
       </c>
-      <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
         <v>0</v>
       </c>
@@ -40838,8 +40688,6 @@
       <c r="K77" t="n">
         <v>1</v>
       </c>
-      <c r="L77" t="inlineStr"/>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
         <v>0</v>
       </c>
@@ -40890,8 +40738,6 @@
       <c r="K78" t="n">
         <v>1</v>
       </c>
-      <c r="L78" t="inlineStr"/>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
         <v>0</v>
       </c>
@@ -40942,8 +40788,6 @@
       <c r="K79" t="n">
         <v>1</v>
       </c>
-      <c r="L79" t="inlineStr"/>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
         <v>0</v>
       </c>
@@ -40994,8 +40838,6 @@
       <c r="K80" t="n">
         <v>1</v>
       </c>
-      <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
         <v>0</v>
       </c>
@@ -41046,8 +40888,6 @@
       <c r="K81" t="n">
         <v>1</v>
       </c>
-      <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
         <v>0</v>
       </c>
@@ -41098,8 +40938,6 @@
       <c r="K82" t="n">
         <v>1</v>
       </c>
-      <c r="L82" t="inlineStr"/>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
         <v>0</v>
       </c>
@@ -41150,8 +40988,6 @@
       <c r="K83" t="n">
         <v>1</v>
       </c>
-      <c r="L83" t="inlineStr"/>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
         <v>0</v>
       </c>
@@ -41202,8 +41038,6 @@
       <c r="K84" t="n">
         <v>1</v>
       </c>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
         <v>0</v>
       </c>
@@ -41254,8 +41088,6 @@
       <c r="K85" t="n">
         <v>1</v>
       </c>
-      <c r="L85" t="inlineStr"/>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
         <v>0</v>
       </c>
@@ -41306,8 +41138,6 @@
       <c r="K86" t="n">
         <v>1</v>
       </c>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
         <v>0</v>
       </c>
@@ -41358,8 +41188,6 @@
       <c r="K87" t="n">
         <v>1</v>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
         <v>0</v>
       </c>
@@ -41410,8 +41238,6 @@
       <c r="K88" t="n">
         <v>1</v>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
         <v>0</v>
       </c>
@@ -41462,8 +41288,6 @@
       <c r="K89" t="n">
         <v>1</v>
       </c>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
         <v>0</v>
       </c>
@@ -41514,8 +41338,6 @@
       <c r="K90" t="n">
         <v>1</v>
       </c>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
         <v>0</v>
       </c>
@@ -41566,8 +41388,6 @@
       <c r="K91" t="n">
         <v>1</v>
       </c>
-      <c r="L91" t="inlineStr"/>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
         <v>0</v>
       </c>
@@ -41618,8 +41438,6 @@
       <c r="K92" t="n">
         <v>1</v>
       </c>
-      <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
         <v>0</v>
       </c>
@@ -41670,8 +41488,6 @@
       <c r="K93" t="n">
         <v>1</v>
       </c>
-      <c r="L93" t="inlineStr"/>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
         <v>0</v>
       </c>
@@ -41722,8 +41538,6 @@
       <c r="K94" t="n">
         <v>1</v>
       </c>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
         <v>0</v>
       </c>
@@ -41774,8 +41588,6 @@
       <c r="K95" t="n">
         <v>1</v>
       </c>
-      <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
         <v>0</v>
       </c>
@@ -41826,8 +41638,6 @@
       <c r="K96" t="n">
         <v>1</v>
       </c>
-      <c r="L96" t="inlineStr"/>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
         <v>0</v>
       </c>
@@ -41878,8 +41688,6 @@
       <c r="K97" t="n">
         <v>1</v>
       </c>
-      <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
         <v>0</v>
       </c>
@@ -41930,8 +41738,6 @@
       <c r="K98" t="n">
         <v>1</v>
       </c>
-      <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
         <v>0</v>
       </c>
@@ -41982,8 +41788,6 @@
       <c r="K99" t="n">
         <v>1</v>
       </c>
-      <c r="L99" t="inlineStr"/>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
         <v>0</v>
       </c>
@@ -42034,8 +41838,6 @@
       <c r="K100" t="n">
         <v>1</v>
       </c>
-      <c r="L100" t="inlineStr"/>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
         <v>0</v>
       </c>
@@ -42086,8 +41888,6 @@
       <c r="K101" t="n">
         <v>1</v>
       </c>
-      <c r="L101" t="inlineStr"/>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
         <v>0</v>
       </c>
@@ -42138,8 +41938,6 @@
       <c r="K102" t="n">
         <v>1</v>
       </c>
-      <c r="L102" t="inlineStr"/>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
         <v>0</v>
       </c>
@@ -42190,8 +41988,6 @@
       <c r="K103" t="n">
         <v>1</v>
       </c>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
         <v>0</v>
       </c>
@@ -42242,8 +42038,6 @@
       <c r="K104" t="n">
         <v>1</v>
       </c>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
         <v>0</v>
       </c>
@@ -42294,8 +42088,6 @@
       <c r="K105" t="n">
         <v>1</v>
       </c>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
         <v>0</v>
       </c>
@@ -42346,8 +42138,6 @@
       <c r="K106" t="n">
         <v>1</v>
       </c>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="n">
         <v>0</v>
       </c>
@@ -42398,8 +42188,6 @@
       <c r="K107" t="n">
         <v>1</v>
       </c>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
         <v>0</v>
       </c>
@@ -42450,8 +42238,6 @@
       <c r="K108" t="n">
         <v>1</v>
       </c>
-      <c r="L108" t="inlineStr"/>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="n">
         <v>0</v>
       </c>
@@ -42502,8 +42288,6 @@
       <c r="K109" t="n">
         <v>1</v>
       </c>
-      <c r="L109" t="inlineStr"/>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
         <v>0</v>
       </c>
@@ -42554,8 +42338,6 @@
       <c r="K110" t="n">
         <v>1</v>
       </c>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="n">
         <v>0</v>
       </c>
@@ -42606,8 +42388,6 @@
       <c r="K111" t="n">
         <v>1</v>
       </c>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
         <v>0</v>
       </c>
@@ -42658,8 +42438,6 @@
       <c r="K112" t="n">
         <v>1</v>
       </c>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="n">
         <v>0</v>
       </c>
@@ -42710,8 +42488,6 @@
       <c r="K113" t="n">
         <v>1</v>
       </c>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
         <v>0</v>
       </c>
@@ -42762,8 +42538,6 @@
       <c r="K114" t="n">
         <v>1</v>
       </c>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
         <v>0</v>
       </c>
@@ -42814,8 +42588,6 @@
       <c r="K115" t="n">
         <v>1</v>
       </c>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
         <v>0</v>
       </c>
@@ -42866,8 +42638,6 @@
       <c r="K116" t="n">
         <v>1</v>
       </c>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="n">
         <v>0</v>
       </c>
@@ -42918,8 +42688,6 @@
       <c r="K117" t="n">
         <v>1</v>
       </c>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
         <v>0</v>
       </c>
@@ -42960,8 +42728,6 @@
       <c r="K118" t="n">
         <v>1</v>
       </c>
-      <c r="L118" t="inlineStr"/>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="n">
         <v>0</v>
       </c>
@@ -43012,8 +42778,6 @@
       <c r="K119" t="n">
         <v>1</v>
       </c>
-      <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="n">
         <v>0</v>
       </c>
@@ -43064,8 +42828,6 @@
       <c r="K120" t="n">
         <v>1</v>
       </c>
-      <c r="L120" t="inlineStr"/>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="n">
         <v>0</v>
       </c>
@@ -43116,8 +42878,6 @@
       <c r="K121" t="n">
         <v>1</v>
       </c>
-      <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
         <v>0</v>
       </c>
@@ -43168,8 +42928,6 @@
       <c r="K122" t="n">
         <v>1</v>
       </c>
-      <c r="L122" t="inlineStr"/>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="n">
         <v>0</v>
       </c>
@@ -43220,8 +42978,6 @@
       <c r="K123" t="n">
         <v>1</v>
       </c>
-      <c r="L123" t="inlineStr"/>
-      <c r="M123" t="inlineStr"/>
       <c r="N123" t="n">
         <v>0</v>
       </c>
@@ -43272,8 +43028,6 @@
       <c r="K124" t="n">
         <v>1</v>
       </c>
-      <c r="L124" t="inlineStr"/>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="n">
         <v>0</v>
       </c>
@@ -43324,8 +43078,6 @@
       <c r="K125" t="n">
         <v>1</v>
       </c>
-      <c r="L125" t="inlineStr"/>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
         <v>0</v>
       </c>
@@ -43376,8 +43128,6 @@
       <c r="K126" t="n">
         <v>1</v>
       </c>
-      <c r="L126" t="inlineStr"/>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="n">
         <v>0</v>
       </c>
@@ -43428,8 +43178,6 @@
       <c r="K127" t="n">
         <v>1</v>
       </c>
-      <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
         <v>0</v>
       </c>
@@ -43480,8 +43228,6 @@
       <c r="K128" t="n">
         <v>1</v>
       </c>
-      <c r="L128" t="inlineStr"/>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="n">
         <v>0</v>
       </c>
@@ -43532,8 +43278,6 @@
       <c r="K129" t="n">
         <v>1</v>
       </c>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
         <v>0</v>
       </c>
@@ -43574,8 +43318,6 @@
       <c r="K130" t="n">
         <v>1</v>
       </c>
-      <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="n">
         <v>0</v>
       </c>
@@ -43626,8 +43368,6 @@
       <c r="K131" t="n">
         <v>1</v>
       </c>
-      <c r="L131" t="inlineStr"/>
-      <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
         <v>0</v>
       </c>
@@ -43678,8 +43418,6 @@
       <c r="K132" t="n">
         <v>1</v>
       </c>
-      <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
         <v>0</v>
       </c>
@@ -43730,8 +43468,6 @@
       <c r="K133" t="n">
         <v>1</v>
       </c>
-      <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
         <v>0</v>
       </c>
@@ -43782,8 +43518,6 @@
       <c r="K134" t="n">
         <v>1</v>
       </c>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
         <v>0</v>
       </c>
@@ -43834,8 +43568,6 @@
       <c r="K135" t="n">
         <v>1</v>
       </c>
-      <c r="L135" t="inlineStr"/>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
         <v>0</v>
       </c>
@@ -43886,8 +43618,6 @@
       <c r="K136" t="n">
         <v>1</v>
       </c>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
         <v>0</v>
       </c>
@@ -43938,8 +43668,6 @@
       <c r="K137" t="n">
         <v>1</v>
       </c>
-      <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
         <v>0</v>
       </c>
@@ -43990,8 +43718,6 @@
       <c r="K138" t="n">
         <v>1</v>
       </c>
-      <c r="L138" t="inlineStr"/>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="n">
         <v>0</v>
       </c>
@@ -44032,8 +43758,6 @@
       <c r="K139" t="n">
         <v>1</v>
       </c>
-      <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
         <v>0</v>
       </c>
@@ -44084,8 +43808,6 @@
       <c r="K140" t="n">
         <v>1</v>
       </c>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
         <v>0</v>
       </c>
@@ -44136,8 +43858,6 @@
       <c r="K141" t="n">
         <v>1</v>
       </c>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
         <v>0</v>
       </c>
@@ -44188,8 +43908,6 @@
       <c r="K142" t="n">
         <v>1</v>
       </c>
-      <c r="L142" t="inlineStr"/>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="n">
         <v>0</v>
       </c>
@@ -44240,8 +43958,6 @@
       <c r="K143" t="n">
         <v>1</v>
       </c>
-      <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
         <v>0</v>
       </c>
@@ -44292,8 +44008,6 @@
       <c r="K144" t="n">
         <v>1</v>
       </c>
-      <c r="L144" t="inlineStr"/>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="n">
         <v>0</v>
       </c>
@@ -44334,8 +44048,6 @@
       <c r="K145" t="n">
         <v>1</v>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
         <v>0</v>
       </c>
@@ -44386,8 +44098,6 @@
       <c r="K146" t="n">
         <v>1</v>
       </c>
-      <c r="L146" t="inlineStr"/>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="n">
         <v>0</v>
       </c>
@@ -44428,8 +44138,6 @@
       <c r="K147" t="n">
         <v>1</v>
       </c>
-      <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="n">
         <v>0</v>
       </c>
@@ -44480,8 +44188,6 @@
       <c r="K148" t="n">
         <v>1</v>
       </c>
-      <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="n">
         <v>0</v>
       </c>
@@ -44532,8 +44238,6 @@
       <c r="K149" t="n">
         <v>1</v>
       </c>
-      <c r="L149" t="inlineStr"/>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
         <v>0</v>
       </c>
@@ -44584,8 +44288,6 @@
       <c r="K150" t="n">
         <v>1</v>
       </c>
-      <c r="L150" t="inlineStr"/>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="n">
         <v>0</v>
       </c>
@@ -44636,8 +44338,6 @@
       <c r="K151" t="n">
         <v>1</v>
       </c>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="n">
         <v>0</v>
       </c>
@@ -44688,8 +44388,6 @@
       <c r="K152" t="n">
         <v>1</v>
       </c>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="n">
         <v>0</v>
       </c>
@@ -44740,8 +44438,6 @@
       <c r="K153" t="n">
         <v>1</v>
       </c>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
       <c r="N153" t="n">
         <v>0</v>
       </c>
@@ -44792,8 +44488,6 @@
       <c r="K154" t="n">
         <v>1</v>
       </c>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
       <c r="N154" t="n">
         <v>0</v>
       </c>
@@ -44844,8 +44538,6 @@
       <c r="K155" t="n">
         <v>1</v>
       </c>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
       <c r="N155" t="n">
         <v>0</v>
       </c>
@@ -44896,8 +44588,6 @@
       <c r="K156" t="n">
         <v>1</v>
       </c>
-      <c r="L156" t="inlineStr"/>
-      <c r="M156" t="inlineStr"/>
       <c r="N156" t="n">
         <v>0</v>
       </c>
@@ -44948,8 +44638,6 @@
       <c r="K157" t="n">
         <v>1</v>
       </c>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr"/>
       <c r="N157" t="n">
         <v>0</v>
       </c>
@@ -45000,8 +44688,6 @@
       <c r="K158" t="n">
         <v>1</v>
       </c>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="n">
         <v>0</v>
       </c>
@@ -45052,8 +44738,6 @@
       <c r="K159" t="n">
         <v>1</v>
       </c>
-      <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
       <c r="N159" t="n">
         <v>0</v>
       </c>
@@ -45104,8 +44788,6 @@
       <c r="K160" t="n">
         <v>1</v>
       </c>
-      <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="n">
         <v>0</v>
       </c>
@@ -45156,8 +44838,6 @@
       <c r="K161" t="n">
         <v>1</v>
       </c>
-      <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
       <c r="N161" t="n">
         <v>0</v>
       </c>
@@ -45208,8 +44888,6 @@
       <c r="K162" t="n">
         <v>1</v>
       </c>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
       <c r="N162" t="n">
         <v>0</v>
       </c>
@@ -45260,8 +44938,6 @@
       <c r="K163" t="n">
         <v>1</v>
       </c>
-      <c r="L163" t="inlineStr"/>
-      <c r="M163" t="inlineStr"/>
       <c r="N163" t="n">
         <v>0</v>
       </c>
@@ -45312,8 +44988,6 @@
       <c r="K164" t="n">
         <v>1</v>
       </c>
-      <c r="L164" t="inlineStr"/>
-      <c r="M164" t="inlineStr"/>
       <c r="N164" t="n">
         <v>0</v>
       </c>
@@ -45364,8 +45038,6 @@
       <c r="K165" t="n">
         <v>1</v>
       </c>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
         <v>0</v>
       </c>
@@ -45416,8 +45088,6 @@
       <c r="K166" t="n">
         <v>1</v>
       </c>
-      <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr"/>
       <c r="N166" t="n">
         <v>0</v>
       </c>
@@ -45468,8 +45138,6 @@
       <c r="K167" t="n">
         <v>1</v>
       </c>
-      <c r="L167" t="inlineStr"/>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="n">
         <v>0</v>
       </c>
@@ -45520,8 +45188,6 @@
       <c r="K168" t="n">
         <v>1</v>
       </c>
-      <c r="L168" t="inlineStr"/>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="n">
         <v>0</v>
       </c>
@@ -45572,8 +45238,6 @@
       <c r="K169" t="n">
         <v>1</v>
       </c>
-      <c r="L169" t="inlineStr"/>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="n">
         <v>0</v>
       </c>
@@ -45624,8 +45288,6 @@
       <c r="K170" t="n">
         <v>1</v>
       </c>
-      <c r="L170" t="inlineStr"/>
-      <c r="M170" t="inlineStr"/>
       <c r="N170" t="n">
         <v>0</v>
       </c>
@@ -45676,8 +45338,6 @@
       <c r="K171" t="n">
         <v>1</v>
       </c>
-      <c r="L171" t="inlineStr"/>
-      <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
         <v>0</v>
       </c>
@@ -45728,8 +45388,6 @@
       <c r="K172" t="n">
         <v>1</v>
       </c>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="n">
         <v>0</v>
       </c>
@@ -45780,8 +45438,6 @@
       <c r="K173" t="n">
         <v>1</v>
       </c>
-      <c r="L173" t="inlineStr"/>
-      <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
         <v>0</v>
       </c>
@@ -45822,8 +45478,6 @@
       <c r="K174" t="n">
         <v>1</v>
       </c>
-      <c r="L174" t="inlineStr"/>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="n">
         <v>0</v>
       </c>
@@ -45874,8 +45528,6 @@
       <c r="K175" t="n">
         <v>1</v>
       </c>
-      <c r="L175" t="inlineStr"/>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
         <v>0</v>
       </c>
@@ -45926,8 +45578,6 @@
       <c r="K176" t="n">
         <v>1</v>
       </c>
-      <c r="L176" t="inlineStr"/>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="n">
         <v>0</v>
       </c>
@@ -45978,8 +45628,6 @@
       <c r="K177" t="n">
         <v>1</v>
       </c>
-      <c r="L177" t="inlineStr"/>
-      <c r="M177" t="inlineStr"/>
       <c r="N177" t="n">
         <v>0</v>
       </c>
@@ -46030,8 +45678,6 @@
       <c r="K178" t="n">
         <v>1</v>
       </c>
-      <c r="L178" t="inlineStr"/>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="n">
         <v>0</v>
       </c>
@@ -46082,8 +45728,6 @@
       <c r="K179" t="n">
         <v>1</v>
       </c>
-      <c r="L179" t="inlineStr"/>
-      <c r="M179" t="inlineStr"/>
       <c r="N179" t="n">
         <v>0</v>
       </c>
@@ -46134,8 +45778,6 @@
       <c r="K180" t="n">
         <v>1</v>
       </c>
-      <c r="L180" t="inlineStr"/>
-      <c r="M180" t="inlineStr"/>
       <c r="N180" t="n">
         <v>0</v>
       </c>
@@ -46186,8 +45828,6 @@
       <c r="K181" t="n">
         <v>1</v>
       </c>
-      <c r="L181" t="inlineStr"/>
-      <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
         <v>0</v>
       </c>
@@ -46238,8 +45878,6 @@
       <c r="K182" t="n">
         <v>1</v>
       </c>
-      <c r="L182" t="inlineStr"/>
-      <c r="M182" t="inlineStr"/>
       <c r="N182" t="n">
         <v>0</v>
       </c>
@@ -46290,8 +45928,6 @@
       <c r="K183" t="n">
         <v>1</v>
       </c>
-      <c r="L183" t="inlineStr"/>
-      <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
         <v>0</v>
       </c>
@@ -46342,8 +45978,6 @@
       <c r="K184" t="n">
         <v>1</v>
       </c>
-      <c r="L184" t="inlineStr"/>
-      <c r="M184" t="inlineStr"/>
       <c r="N184" t="n">
         <v>0</v>
       </c>
@@ -46394,8 +46028,6 @@
       <c r="K185" t="n">
         <v>1</v>
       </c>
-      <c r="L185" t="inlineStr"/>
-      <c r="M185" t="inlineStr"/>
       <c r="N185" t="n">
         <v>0</v>
       </c>
@@ -46446,8 +46078,6 @@
       <c r="K186" t="n">
         <v>1</v>
       </c>
-      <c r="L186" t="inlineStr"/>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="n">
         <v>0</v>
       </c>
@@ -46498,8 +46128,6 @@
       <c r="K187" t="n">
         <v>1</v>
       </c>
-      <c r="L187" t="inlineStr"/>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="n">
         <v>0</v>
       </c>
@@ -46550,8 +46178,6 @@
       <c r="K188" t="n">
         <v>1</v>
       </c>
-      <c r="L188" t="inlineStr"/>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="n">
         <v>0</v>
       </c>
@@ -46602,8 +46228,6 @@
       <c r="K189" t="n">
         <v>1</v>
       </c>
-      <c r="L189" t="inlineStr"/>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
         <v>0</v>
       </c>
@@ -46654,8 +46278,6 @@
       <c r="K190" t="n">
         <v>1</v>
       </c>
-      <c r="L190" t="inlineStr"/>
-      <c r="M190" t="inlineStr"/>
       <c r="N190" t="n">
         <v>0</v>
       </c>
@@ -46706,8 +46328,6 @@
       <c r="K191" t="n">
         <v>1</v>
       </c>
-      <c r="L191" t="inlineStr"/>
-      <c r="M191" t="inlineStr"/>
       <c r="N191" t="n">
         <v>0</v>
       </c>
@@ -46758,8 +46378,6 @@
       <c r="K192" t="n">
         <v>1</v>
       </c>
-      <c r="L192" t="inlineStr"/>
-      <c r="M192" t="inlineStr"/>
       <c r="N192" t="n">
         <v>0</v>
       </c>
@@ -46810,8 +46428,6 @@
       <c r="K193" t="n">
         <v>1</v>
       </c>
-      <c r="L193" t="inlineStr"/>
-      <c r="M193" t="inlineStr"/>
       <c r="N193" t="n">
         <v>0</v>
       </c>
@@ -46862,8 +46478,6 @@
       <c r="K194" t="n">
         <v>1</v>
       </c>
-      <c r="L194" t="inlineStr"/>
-      <c r="M194" t="inlineStr"/>
       <c r="N194" t="n">
         <v>0</v>
       </c>
@@ -46904,8 +46518,6 @@
       <c r="K195" t="n">
         <v>1</v>
       </c>
-      <c r="L195" t="inlineStr"/>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="n">
         <v>0</v>
       </c>
@@ -46946,8 +46558,6 @@
       <c r="K196" t="n">
         <v>1</v>
       </c>
-      <c r="L196" t="inlineStr"/>
-      <c r="M196" t="inlineStr"/>
       <c r="N196" t="n">
         <v>0</v>
       </c>
@@ -46988,8 +46598,6 @@
       <c r="K197" t="n">
         <v>1</v>
       </c>
-      <c r="L197" t="inlineStr"/>
-      <c r="M197" t="inlineStr"/>
       <c r="N197" t="n">
         <v>0</v>
       </c>
@@ -47040,8 +46648,6 @@
       <c r="K198" t="n">
         <v>1</v>
       </c>
-      <c r="L198" t="inlineStr"/>
-      <c r="M198" t="inlineStr"/>
       <c r="N198" t="n">
         <v>0</v>
       </c>
@@ -47092,8 +46698,6 @@
       <c r="K199" t="n">
         <v>1</v>
       </c>
-      <c r="L199" t="inlineStr"/>
-      <c r="M199" t="inlineStr"/>
       <c r="N199" t="n">
         <v>0</v>
       </c>
@@ -47144,8 +46748,6 @@
       <c r="K200" t="n">
         <v>1</v>
       </c>
-      <c r="L200" t="inlineStr"/>
-      <c r="M200" t="inlineStr"/>
       <c r="N200" t="n">
         <v>0</v>
       </c>
@@ -47196,8 +46798,6 @@
       <c r="K201" t="n">
         <v>1</v>
       </c>
-      <c r="L201" t="inlineStr"/>
-      <c r="M201" t="inlineStr"/>
       <c r="N201" t="n">
         <v>0</v>
       </c>
@@ -47248,8 +46848,6 @@
       <c r="K202" t="n">
         <v>1</v>
       </c>
-      <c r="L202" t="inlineStr"/>
-      <c r="M202" t="inlineStr"/>
       <c r="N202" t="n">
         <v>0</v>
       </c>
@@ -47300,8 +46898,6 @@
       <c r="K203" t="n">
         <v>1</v>
       </c>
-      <c r="L203" t="inlineStr"/>
-      <c r="M203" t="inlineStr"/>
       <c r="N203" t="n">
         <v>0</v>
       </c>
@@ -47352,8 +46948,6 @@
       <c r="K204" t="n">
         <v>1</v>
       </c>
-      <c r="L204" t="inlineStr"/>
-      <c r="M204" t="inlineStr"/>
       <c r="N204" t="n">
         <v>0</v>
       </c>
@@ -47404,8 +46998,6 @@
       <c r="K205" t="n">
         <v>1</v>
       </c>
-      <c r="L205" t="inlineStr"/>
-      <c r="M205" t="inlineStr"/>
       <c r="N205" t="n">
         <v>0</v>
       </c>
@@ -47456,8 +47048,6 @@
       <c r="K206" t="n">
         <v>1</v>
       </c>
-      <c r="L206" t="inlineStr"/>
-      <c r="M206" t="inlineStr"/>
       <c r="N206" t="n">
         <v>0</v>
       </c>
@@ -47508,8 +47098,6 @@
       <c r="K207" t="n">
         <v>1</v>
       </c>
-      <c r="L207" t="inlineStr"/>
-      <c r="M207" t="inlineStr"/>
       <c r="N207" t="n">
         <v>0</v>
       </c>
@@ -47550,8 +47138,6 @@
       <c r="K208" t="n">
         <v>1</v>
       </c>
-      <c r="L208" t="inlineStr"/>
-      <c r="M208" t="inlineStr"/>
       <c r="N208" t="n">
         <v>0</v>
       </c>
@@ -47602,8 +47188,6 @@
       <c r="K209" t="n">
         <v>1</v>
       </c>
-      <c r="L209" t="inlineStr"/>
-      <c r="M209" t="inlineStr"/>
       <c r="N209" t="n">
         <v>0</v>
       </c>
@@ -47654,8 +47238,6 @@
       <c r="K210" t="n">
         <v>1</v>
       </c>
-      <c r="L210" t="inlineStr"/>
-      <c r="M210" t="inlineStr"/>
       <c r="N210" t="n">
         <v>0</v>
       </c>
@@ -47706,8 +47288,6 @@
       <c r="K211" t="n">
         <v>1</v>
       </c>
-      <c r="L211" t="inlineStr"/>
-      <c r="M211" t="inlineStr"/>
       <c r="N211" t="n">
         <v>0</v>
       </c>
@@ -47758,8 +47338,6 @@
       <c r="K212" t="n">
         <v>1</v>
       </c>
-      <c r="L212" t="inlineStr"/>
-      <c r="M212" t="inlineStr"/>
       <c r="N212" t="n">
         <v>0</v>
       </c>
@@ -47810,8 +47388,6 @@
       <c r="K213" t="n">
         <v>1</v>
       </c>
-      <c r="L213" t="inlineStr"/>
-      <c r="M213" t="inlineStr"/>
       <c r="N213" t="n">
         <v>0</v>
       </c>
@@ -47852,8 +47428,6 @@
       <c r="K214" t="n">
         <v>1</v>
       </c>
-      <c r="L214" t="inlineStr"/>
-      <c r="M214" t="inlineStr"/>
       <c r="N214" t="n">
         <v>0</v>
       </c>
@@ -47904,8 +47478,6 @@
       <c r="K215" t="n">
         <v>1</v>
       </c>
-      <c r="L215" t="inlineStr"/>
-      <c r="M215" t="inlineStr"/>
       <c r="N215" t="n">
         <v>0</v>
       </c>
@@ -47956,8 +47528,6 @@
       <c r="K216" t="n">
         <v>1</v>
       </c>
-      <c r="L216" t="inlineStr"/>
-      <c r="M216" t="inlineStr"/>
       <c r="N216" t="n">
         <v>0</v>
       </c>
@@ -48008,8 +47578,6 @@
       <c r="K217" t="n">
         <v>1</v>
       </c>
-      <c r="L217" t="inlineStr"/>
-      <c r="M217" t="inlineStr"/>
       <c r="N217" t="n">
         <v>0</v>
       </c>
@@ -48060,8 +47628,6 @@
       <c r="K218" t="n">
         <v>1</v>
       </c>
-      <c r="L218" t="inlineStr"/>
-      <c r="M218" t="inlineStr"/>
       <c r="N218" t="n">
         <v>0</v>
       </c>
@@ -48112,8 +47678,6 @@
       <c r="K219" t="n">
         <v>1</v>
       </c>
-      <c r="L219" t="inlineStr"/>
-      <c r="M219" t="inlineStr"/>
       <c r="N219" t="n">
         <v>0</v>
       </c>
@@ -48164,8 +47728,6 @@
       <c r="K220" t="n">
         <v>1</v>
       </c>
-      <c r="L220" t="inlineStr"/>
-      <c r="M220" t="inlineStr"/>
       <c r="N220" t="n">
         <v>0</v>
       </c>
@@ -48206,8 +47768,6 @@
       <c r="K221" t="n">
         <v>1</v>
       </c>
-      <c r="L221" t="inlineStr"/>
-      <c r="M221" t="inlineStr"/>
       <c r="N221" t="n">
         <v>0</v>
       </c>
@@ -48258,8 +47818,6 @@
       <c r="K222" t="n">
         <v>1</v>
       </c>
-      <c r="L222" t="inlineStr"/>
-      <c r="M222" t="inlineStr"/>
       <c r="N222" t="n">
         <v>0</v>
       </c>
@@ -48310,8 +47868,6 @@
       <c r="K223" t="n">
         <v>1</v>
       </c>
-      <c r="L223" t="inlineStr"/>
-      <c r="M223" t="inlineStr"/>
       <c r="N223" t="n">
         <v>0</v>
       </c>
@@ -48362,8 +47918,6 @@
       <c r="K224" t="n">
         <v>1</v>
       </c>
-      <c r="L224" t="inlineStr"/>
-      <c r="M224" t="inlineStr"/>
       <c r="N224" t="n">
         <v>0</v>
       </c>
@@ -48414,8 +47968,6 @@
       <c r="K225" t="n">
         <v>1</v>
       </c>
-      <c r="L225" t="inlineStr"/>
-      <c r="M225" t="inlineStr"/>
       <c r="N225" t="n">
         <v>0</v>
       </c>
@@ -48466,8 +48018,6 @@
       <c r="K226" t="n">
         <v>1</v>
       </c>
-      <c r="L226" t="inlineStr"/>
-      <c r="M226" t="inlineStr"/>
       <c r="N226" t="n">
         <v>0</v>
       </c>
@@ -48518,8 +48068,6 @@
       <c r="K227" t="n">
         <v>1</v>
       </c>
-      <c r="L227" t="inlineStr"/>
-      <c r="M227" t="inlineStr"/>
       <c r="N227" t="n">
         <v>0</v>
       </c>
@@ -48570,8 +48118,6 @@
       <c r="K228" t="n">
         <v>1</v>
       </c>
-      <c r="L228" t="inlineStr"/>
-      <c r="M228" t="inlineStr"/>
       <c r="N228" t="n">
         <v>0</v>
       </c>
@@ -48622,8 +48168,6 @@
       <c r="K229" t="n">
         <v>1</v>
       </c>
-      <c r="L229" t="inlineStr"/>
-      <c r="M229" t="inlineStr"/>
       <c r="N229" t="n">
         <v>0</v>
       </c>
@@ -48674,8 +48218,6 @@
       <c r="K230" t="n">
         <v>1</v>
       </c>
-      <c r="L230" t="inlineStr"/>
-      <c r="M230" t="inlineStr"/>
       <c r="N230" t="n">
         <v>0</v>
       </c>
@@ -48716,8 +48258,6 @@
       <c r="K231" t="n">
         <v>1</v>
       </c>
-      <c r="L231" t="inlineStr"/>
-      <c r="M231" t="inlineStr"/>
       <c r="N231" t="n">
         <v>0</v>
       </c>
@@ -48758,8 +48298,6 @@
       <c r="K232" t="n">
         <v>1</v>
       </c>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr"/>
       <c r="N232" t="n">
         <v>0</v>
       </c>
@@ -48800,8 +48338,6 @@
       <c r="K233" t="n">
         <v>1</v>
       </c>
-      <c r="L233" t="inlineStr"/>
-      <c r="M233" t="inlineStr"/>
       <c r="N233" t="n">
         <v>0</v>
       </c>
@@ -48852,8 +48388,6 @@
       <c r="K234" t="n">
         <v>1</v>
       </c>
-      <c r="L234" t="inlineStr"/>
-      <c r="M234" t="inlineStr"/>
       <c r="N234" t="n">
         <v>0</v>
       </c>
@@ -48904,8 +48438,6 @@
       <c r="K235" t="n">
         <v>1</v>
       </c>
-      <c r="L235" t="inlineStr"/>
-      <c r="M235" t="inlineStr"/>
       <c r="N235" t="n">
         <v>0</v>
       </c>
@@ -48956,8 +48488,6 @@
       <c r="K236" t="n">
         <v>1</v>
       </c>
-      <c r="L236" t="inlineStr"/>
-      <c r="M236" t="inlineStr"/>
       <c r="N236" t="n">
         <v>0</v>
       </c>
@@ -49008,8 +48538,6 @@
       <c r="K237" t="n">
         <v>1</v>
       </c>
-      <c r="L237" t="inlineStr"/>
-      <c r="M237" t="inlineStr"/>
       <c r="N237" t="n">
         <v>0</v>
       </c>
@@ -49060,8 +48588,6 @@
       <c r="K238" t="n">
         <v>1</v>
       </c>
-      <c r="L238" t="inlineStr"/>
-      <c r="M238" t="inlineStr"/>
       <c r="N238" t="n">
         <v>0</v>
       </c>
@@ -49112,8 +48638,6 @@
       <c r="K239" t="n">
         <v>1</v>
       </c>
-      <c r="L239" t="inlineStr"/>
-      <c r="M239" t="inlineStr"/>
       <c r="N239" t="n">
         <v>0</v>
       </c>
@@ -49164,8 +48688,6 @@
       <c r="K240" t="n">
         <v>1</v>
       </c>
-      <c r="L240" t="inlineStr"/>
-      <c r="M240" t="inlineStr"/>
       <c r="N240" t="n">
         <v>0</v>
       </c>
@@ -49216,8 +48738,6 @@
       <c r="K241" t="n">
         <v>1</v>
       </c>
-      <c r="L241" t="inlineStr"/>
-      <c r="M241" t="inlineStr"/>
       <c r="N241" t="n">
         <v>0</v>
       </c>
@@ -49268,8 +48788,6 @@
       <c r="K242" t="n">
         <v>1</v>
       </c>
-      <c r="L242" t="inlineStr"/>
-      <c r="M242" t="inlineStr"/>
       <c r="N242" t="n">
         <v>0</v>
       </c>
@@ -49320,8 +48838,6 @@
       <c r="K243" t="n">
         <v>1</v>
       </c>
-      <c r="L243" t="inlineStr"/>
-      <c r="M243" t="inlineStr"/>
       <c r="N243" t="n">
         <v>0</v>
       </c>
@@ -49372,8 +48888,6 @@
       <c r="K244" t="n">
         <v>1</v>
       </c>
-      <c r="L244" t="inlineStr"/>
-      <c r="M244" t="inlineStr"/>
       <c r="N244" t="n">
         <v>0</v>
       </c>
@@ -49424,8 +48938,6 @@
       <c r="K245" t="n">
         <v>1</v>
       </c>
-      <c r="L245" t="inlineStr"/>
-      <c r="M245" t="inlineStr"/>
       <c r="N245" t="n">
         <v>0</v>
       </c>
@@ -49476,8 +48988,6 @@
       <c r="K246" t="n">
         <v>1</v>
       </c>
-      <c r="L246" t="inlineStr"/>
-      <c r="M246" t="inlineStr"/>
       <c r="N246" t="n">
         <v>0</v>
       </c>
@@ -49528,8 +49038,6 @@
       <c r="K247" t="n">
         <v>1</v>
       </c>
-      <c r="L247" t="inlineStr"/>
-      <c r="M247" t="inlineStr"/>
       <c r="N247" t="n">
         <v>0</v>
       </c>
@@ -49580,8 +49088,6 @@
       <c r="K248" t="n">
         <v>1</v>
       </c>
-      <c r="L248" t="inlineStr"/>
-      <c r="M248" t="inlineStr"/>
       <c r="N248" t="n">
         <v>0</v>
       </c>
@@ -49632,8 +49138,6 @@
       <c r="K249" t="n">
         <v>1</v>
       </c>
-      <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr"/>
       <c r="N249" t="n">
         <v>0</v>
       </c>
@@ -49684,8 +49188,6 @@
       <c r="K250" t="n">
         <v>1</v>
       </c>
-      <c r="L250" t="inlineStr"/>
-      <c r="M250" t="inlineStr"/>
       <c r="N250" t="n">
         <v>0</v>
       </c>
@@ -49736,8 +49238,6 @@
       <c r="K251" t="n">
         <v>1</v>
       </c>
-      <c r="L251" t="inlineStr"/>
-      <c r="M251" t="inlineStr"/>
       <c r="N251" t="n">
         <v>0</v>
       </c>
@@ -49788,8 +49288,6 @@
       <c r="K252" t="n">
         <v>1</v>
       </c>
-      <c r="L252" t="inlineStr"/>
-      <c r="M252" t="inlineStr"/>
       <c r="N252" t="n">
         <v>0</v>
       </c>
@@ -49840,8 +49338,6 @@
       <c r="K253" t="n">
         <v>1</v>
       </c>
-      <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr"/>
       <c r="N253" t="n">
         <v>0</v>
       </c>
@@ -49892,8 +49388,6 @@
       <c r="K254" t="n">
         <v>1</v>
       </c>
-      <c r="L254" t="inlineStr"/>
-      <c r="M254" t="inlineStr"/>
       <c r="N254" t="n">
         <v>0</v>
       </c>
@@ -49944,8 +49438,6 @@
       <c r="K255" t="n">
         <v>1</v>
       </c>
-      <c r="L255" t="inlineStr"/>
-      <c r="M255" t="inlineStr"/>
       <c r="N255" t="n">
         <v>0</v>
       </c>
@@ -49996,8 +49488,6 @@
       <c r="K256" t="n">
         <v>1</v>
       </c>
-      <c r="L256" t="inlineStr"/>
-      <c r="M256" t="inlineStr"/>
       <c r="N256" t="n">
         <v>0</v>
       </c>
@@ -50048,8 +49538,6 @@
       <c r="K257" t="n">
         <v>1</v>
       </c>
-      <c r="L257" t="inlineStr"/>
-      <c r="M257" t="inlineStr"/>
       <c r="N257" t="n">
         <v>0</v>
       </c>
@@ -50100,8 +49588,6 @@
       <c r="K258" t="n">
         <v>1</v>
       </c>
-      <c r="L258" t="inlineStr"/>
-      <c r="M258" t="inlineStr"/>
       <c r="N258" t="n">
         <v>0</v>
       </c>
@@ -50152,8 +49638,6 @@
       <c r="K259" t="n">
         <v>1</v>
       </c>
-      <c r="L259" t="inlineStr"/>
-      <c r="M259" t="inlineStr"/>
       <c r="N259" t="n">
         <v>0</v>
       </c>
@@ -50204,8 +49688,6 @@
       <c r="K260" t="n">
         <v>1</v>
       </c>
-      <c r="L260" t="inlineStr"/>
-      <c r="M260" t="inlineStr"/>
       <c r="N260" t="n">
         <v>0</v>
       </c>
@@ -50256,8 +49738,6 @@
       <c r="K261" t="n">
         <v>1</v>
       </c>
-      <c r="L261" t="inlineStr"/>
-      <c r="M261" t="inlineStr"/>
       <c r="N261" t="n">
         <v>0</v>
       </c>
@@ -50308,8 +49788,6 @@
       <c r="K262" t="n">
         <v>1</v>
       </c>
-      <c r="L262" t="inlineStr"/>
-      <c r="M262" t="inlineStr"/>
       <c r="N262" t="n">
         <v>0</v>
       </c>
@@ -50360,8 +49838,6 @@
       <c r="K263" t="n">
         <v>1</v>
       </c>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr"/>
       <c r="N263" t="n">
         <v>0</v>
       </c>
@@ -50412,8 +49888,6 @@
       <c r="K264" t="n">
         <v>1</v>
       </c>
-      <c r="L264" t="inlineStr"/>
-      <c r="M264" t="inlineStr"/>
       <c r="N264" t="n">
         <v>0</v>
       </c>
@@ -50464,8 +49938,6 @@
       <c r="K265" t="n">
         <v>1</v>
       </c>
-      <c r="L265" t="inlineStr"/>
-      <c r="M265" t="inlineStr"/>
       <c r="N265" t="n">
         <v>0</v>
       </c>
@@ -50516,8 +49988,6 @@
       <c r="K266" t="n">
         <v>1</v>
       </c>
-      <c r="L266" t="inlineStr"/>
-      <c r="M266" t="inlineStr"/>
       <c r="N266" t="n">
         <v>0</v>
       </c>
@@ -50568,8 +50038,6 @@
       <c r="K267" t="n">
         <v>1</v>
       </c>
-      <c r="L267" t="inlineStr"/>
-      <c r="M267" t="inlineStr"/>
       <c r="N267" t="n">
         <v>0</v>
       </c>
@@ -50620,8 +50088,6 @@
       <c r="K268" t="n">
         <v>1</v>
       </c>
-      <c r="L268" t="inlineStr"/>
-      <c r="M268" t="inlineStr"/>
       <c r="N268" t="n">
         <v>0</v>
       </c>
@@ -50672,8 +50138,6 @@
       <c r="K269" t="n">
         <v>1</v>
       </c>
-      <c r="L269" t="inlineStr"/>
-      <c r="M269" t="inlineStr"/>
       <c r="N269" t="n">
         <v>0</v>
       </c>
@@ -50724,8 +50188,6 @@
       <c r="K270" t="n">
         <v>1</v>
       </c>
-      <c r="L270" t="inlineStr"/>
-      <c r="M270" t="inlineStr"/>
       <c r="N270" t="n">
         <v>0</v>
       </c>
@@ -50776,8 +50238,6 @@
       <c r="K271" t="n">
         <v>1</v>
       </c>
-      <c r="L271" t="inlineStr"/>
-      <c r="M271" t="inlineStr"/>
       <c r="N271" t="n">
         <v>0</v>
       </c>
@@ -50828,8 +50288,6 @@
       <c r="K272" t="n">
         <v>1</v>
       </c>
-      <c r="L272" t="inlineStr"/>
-      <c r="M272" t="inlineStr"/>
       <c r="N272" t="n">
         <v>0</v>
       </c>
@@ -50880,8 +50338,6 @@
       <c r="K273" t="n">
         <v>1</v>
       </c>
-      <c r="L273" t="inlineStr"/>
-      <c r="M273" t="inlineStr"/>
       <c r="N273" t="n">
         <v>0</v>
       </c>
@@ -50932,8 +50388,6 @@
       <c r="K274" t="n">
         <v>1</v>
       </c>
-      <c r="L274" t="inlineStr"/>
-      <c r="M274" t="inlineStr"/>
       <c r="N274" t="n">
         <v>0</v>
       </c>
@@ -50984,8 +50438,6 @@
       <c r="K275" t="n">
         <v>1</v>
       </c>
-      <c r="L275" t="inlineStr"/>
-      <c r="M275" t="inlineStr"/>
       <c r="N275" t="n">
         <v>0</v>
       </c>
@@ -51036,8 +50488,6 @@
       <c r="K276" t="n">
         <v>1</v>
       </c>
-      <c r="L276" t="inlineStr"/>
-      <c r="M276" t="inlineStr"/>
       <c r="N276" t="n">
         <v>0</v>
       </c>
@@ -51088,8 +50538,6 @@
       <c r="K277" t="n">
         <v>1</v>
       </c>
-      <c r="L277" t="inlineStr"/>
-      <c r="M277" t="inlineStr"/>
       <c r="N277" t="n">
         <v>0</v>
       </c>
@@ -51140,8 +50588,6 @@
       <c r="K278" t="n">
         <v>1</v>
       </c>
-      <c r="L278" t="inlineStr"/>
-      <c r="M278" t="inlineStr"/>
       <c r="N278" t="n">
         <v>0</v>
       </c>
@@ -51192,8 +50638,6 @@
       <c r="K279" t="n">
         <v>1</v>
       </c>
-      <c r="L279" t="inlineStr"/>
-      <c r="M279" t="inlineStr"/>
       <c r="N279" t="n">
         <v>0</v>
       </c>
@@ -51244,8 +50688,6 @@
       <c r="K280" t="n">
         <v>1</v>
       </c>
-      <c r="L280" t="inlineStr"/>
-      <c r="M280" t="inlineStr"/>
       <c r="N280" t="n">
         <v>0</v>
       </c>
@@ -51286,8 +50728,6 @@
       <c r="K281" t="n">
         <v>1</v>
       </c>
-      <c r="L281" t="inlineStr"/>
-      <c r="M281" t="inlineStr"/>
       <c r="N281" t="n">
         <v>0</v>
       </c>
@@ -51338,8 +50778,6 @@
       <c r="K282" t="n">
         <v>1</v>
       </c>
-      <c r="L282" t="inlineStr"/>
-      <c r="M282" t="inlineStr"/>
       <c r="N282" t="n">
         <v>0</v>
       </c>
@@ -51390,8 +50828,6 @@
       <c r="K283" t="n">
         <v>1</v>
       </c>
-      <c r="L283" t="inlineStr"/>
-      <c r="M283" t="inlineStr"/>
       <c r="N283" t="n">
         <v>0</v>
       </c>
@@ -51442,8 +50878,6 @@
       <c r="K284" t="n">
         <v>1</v>
       </c>
-      <c r="L284" t="inlineStr"/>
-      <c r="M284" t="inlineStr"/>
       <c r="N284" t="n">
         <v>0</v>
       </c>
@@ -51494,8 +50928,6 @@
       <c r="K285" t="n">
         <v>1</v>
       </c>
-      <c r="L285" t="inlineStr"/>
-      <c r="M285" t="inlineStr"/>
       <c r="N285" t="n">
         <v>0</v>
       </c>
@@ -51546,8 +50978,6 @@
       <c r="K286" t="n">
         <v>1</v>
       </c>
-      <c r="L286" t="inlineStr"/>
-      <c r="M286" t="inlineStr"/>
       <c r="N286" t="n">
         <v>0</v>
       </c>
@@ -51598,8 +51028,6 @@
       <c r="K287" t="n">
         <v>1</v>
       </c>
-      <c r="L287" t="inlineStr"/>
-      <c r="M287" t="inlineStr"/>
       <c r="N287" t="n">
         <v>0</v>
       </c>
@@ -51650,8 +51078,6 @@
       <c r="K288" t="n">
         <v>1</v>
       </c>
-      <c r="L288" t="inlineStr"/>
-      <c r="M288" t="inlineStr"/>
       <c r="N288" t="n">
         <v>0</v>
       </c>
@@ -51702,8 +51128,6 @@
       <c r="K289" t="n">
         <v>1</v>
       </c>
-      <c r="L289" t="inlineStr"/>
-      <c r="M289" t="inlineStr"/>
       <c r="N289" t="n">
         <v>0</v>
       </c>
@@ -51754,8 +51178,6 @@
       <c r="K290" t="n">
         <v>1</v>
       </c>
-      <c r="L290" t="inlineStr"/>
-      <c r="M290" t="inlineStr"/>
       <c r="N290" t="n">
         <v>0</v>
       </c>
@@ -51806,8 +51228,6 @@
       <c r="K291" t="n">
         <v>1</v>
       </c>
-      <c r="L291" t="inlineStr"/>
-      <c r="M291" t="inlineStr"/>
       <c r="N291" t="n">
         <v>0</v>
       </c>
@@ -51858,8 +51278,6 @@
       <c r="K292" t="n">
         <v>1</v>
       </c>
-      <c r="L292" t="inlineStr"/>
-      <c r="M292" t="inlineStr"/>
       <c r="N292" t="n">
         <v>0</v>
       </c>
@@ -51910,8 +51328,6 @@
       <c r="K293" t="n">
         <v>1</v>
       </c>
-      <c r="L293" t="inlineStr"/>
-      <c r="M293" t="inlineStr"/>
       <c r="N293" t="n">
         <v>0</v>
       </c>
@@ -51962,8 +51378,6 @@
       <c r="K294" t="n">
         <v>1</v>
       </c>
-      <c r="L294" t="inlineStr"/>
-      <c r="M294" t="inlineStr"/>
       <c r="N294" t="n">
         <v>0</v>
       </c>
@@ -52004,8 +51418,6 @@
       <c r="K295" t="n">
         <v>1</v>
       </c>
-      <c r="L295" t="inlineStr"/>
-      <c r="M295" t="inlineStr"/>
       <c r="N295" t="n">
         <v>0</v>
       </c>
@@ -52056,8 +51468,6 @@
       <c r="K296" t="n">
         <v>1</v>
       </c>
-      <c r="L296" t="inlineStr"/>
-      <c r="M296" t="inlineStr"/>
       <c r="N296" t="n">
         <v>0</v>
       </c>
@@ -52108,8 +51518,6 @@
       <c r="K297" t="n">
         <v>1</v>
       </c>
-      <c r="L297" t="inlineStr"/>
-      <c r="M297" t="inlineStr"/>
       <c r="N297" t="n">
         <v>0</v>
       </c>
@@ -52150,8 +51558,6 @@
       <c r="K298" t="n">
         <v>1</v>
       </c>
-      <c r="L298" t="inlineStr"/>
-      <c r="M298" t="inlineStr"/>
       <c r="N298" t="n">
         <v>0</v>
       </c>
@@ -52192,8 +51598,6 @@
       <c r="K299" t="n">
         <v>1</v>
       </c>
-      <c r="L299" t="inlineStr"/>
-      <c r="M299" t="inlineStr"/>
       <c r="N299" t="n">
         <v>0</v>
       </c>
@@ -52234,8 +51638,6 @@
       <c r="K300" t="n">
         <v>1</v>
       </c>
-      <c r="L300" t="inlineStr"/>
-      <c r="M300" t="inlineStr"/>
       <c r="N300" t="n">
         <v>0</v>
       </c>
@@ -52286,8 +51688,6 @@
       <c r="K301" t="n">
         <v>1</v>
       </c>
-      <c r="L301" t="inlineStr"/>
-      <c r="M301" t="inlineStr"/>
       <c r="N301" t="n">
         <v>0</v>
       </c>
@@ -52328,8 +51728,6 @@
       <c r="K302" t="n">
         <v>1</v>
       </c>
-      <c r="L302" t="inlineStr"/>
-      <c r="M302" t="inlineStr"/>
       <c r="N302" t="n">
         <v>0</v>
       </c>
@@ -52370,8 +51768,6 @@
       <c r="K303" t="n">
         <v>1</v>
       </c>
-      <c r="L303" t="inlineStr"/>
-      <c r="M303" t="inlineStr"/>
       <c r="N303" t="n">
         <v>0</v>
       </c>
@@ -52422,8 +51818,6 @@
       <c r="K304" t="n">
         <v>1</v>
       </c>
-      <c r="L304" t="inlineStr"/>
-      <c r="M304" t="inlineStr"/>
       <c r="N304" t="n">
         <v>0</v>
       </c>
@@ -52474,8 +51868,6 @@
       <c r="K305" t="n">
         <v>1</v>
       </c>
-      <c r="L305" t="inlineStr"/>
-      <c r="M305" t="inlineStr"/>
       <c r="N305" t="n">
         <v>0</v>
       </c>
@@ -52526,8 +51918,6 @@
       <c r="K306" t="n">
         <v>1</v>
       </c>
-      <c r="L306" t="inlineStr"/>
-      <c r="M306" t="inlineStr"/>
       <c r="N306" t="n">
         <v>0</v>
       </c>
@@ -52578,8 +51968,6 @@
       <c r="K307" t="n">
         <v>1</v>
       </c>
-      <c r="L307" t="inlineStr"/>
-      <c r="M307" t="inlineStr"/>
       <c r="N307" t="n">
         <v>0</v>
       </c>
@@ -52630,8 +52018,6 @@
       <c r="K308" t="n">
         <v>1</v>
       </c>
-      <c r="L308" t="inlineStr"/>
-      <c r="M308" t="inlineStr"/>
       <c r="N308" t="n">
         <v>0</v>
       </c>
@@ -52682,8 +52068,6 @@
       <c r="K309" t="n">
         <v>1</v>
       </c>
-      <c r="L309" t="inlineStr"/>
-      <c r="M309" t="inlineStr"/>
       <c r="N309" t="n">
         <v>0</v>
       </c>
@@ -52734,8 +52118,6 @@
       <c r="K310" t="n">
         <v>1</v>
       </c>
-      <c r="L310" t="inlineStr"/>
-      <c r="M310" t="inlineStr"/>
       <c r="N310" t="n">
         <v>0</v>
       </c>
@@ -52786,8 +52168,6 @@
       <c r="K311" t="n">
         <v>1</v>
       </c>
-      <c r="L311" t="inlineStr"/>
-      <c r="M311" t="inlineStr"/>
       <c r="N311" t="n">
         <v>0</v>
       </c>
@@ -52838,8 +52218,6 @@
       <c r="K312" t="n">
         <v>1</v>
       </c>
-      <c r="L312" t="inlineStr"/>
-      <c r="M312" t="inlineStr"/>
       <c r="N312" t="n">
         <v>0</v>
       </c>
@@ -52890,8 +52268,6 @@
       <c r="K313" t="n">
         <v>1</v>
       </c>
-      <c r="L313" t="inlineStr"/>
-      <c r="M313" t="inlineStr"/>
       <c r="N313" t="n">
         <v>0</v>
       </c>
@@ -52942,8 +52318,6 @@
       <c r="K314" t="n">
         <v>1</v>
       </c>
-      <c r="L314" t="inlineStr"/>
-      <c r="M314" t="inlineStr"/>
       <c r="N314" t="n">
         <v>0</v>
       </c>
@@ -52994,8 +52368,6 @@
       <c r="K315" t="n">
         <v>1</v>
       </c>
-      <c r="L315" t="inlineStr"/>
-      <c r="M315" t="inlineStr"/>
       <c r="N315" t="n">
         <v>0</v>
       </c>
@@ -53046,8 +52418,6 @@
       <c r="K316" t="n">
         <v>1</v>
       </c>
-      <c r="L316" t="inlineStr"/>
-      <c r="M316" t="inlineStr"/>
       <c r="N316" t="n">
         <v>0</v>
       </c>
@@ -53098,8 +52468,6 @@
       <c r="K317" t="n">
         <v>1</v>
       </c>
-      <c r="L317" t="inlineStr"/>
-      <c r="M317" t="inlineStr"/>
       <c r="N317" t="n">
         <v>0</v>
       </c>
@@ -53150,8 +52518,6 @@
       <c r="K318" t="n">
         <v>1</v>
       </c>
-      <c r="L318" t="inlineStr"/>
-      <c r="M318" t="inlineStr"/>
       <c r="N318" t="n">
         <v>0</v>
       </c>
@@ -53202,8 +52568,6 @@
       <c r="K319" t="n">
         <v>1</v>
       </c>
-      <c r="L319" t="inlineStr"/>
-      <c r="M319" t="inlineStr"/>
       <c r="N319" t="n">
         <v>0</v>
       </c>
@@ -53254,8 +52618,6 @@
       <c r="K320" t="n">
         <v>1</v>
       </c>
-      <c r="L320" t="inlineStr"/>
-      <c r="M320" t="inlineStr"/>
       <c r="N320" t="n">
         <v>0</v>
       </c>
@@ -53306,8 +52668,6 @@
       <c r="K321" t="n">
         <v>1</v>
       </c>
-      <c r="L321" t="inlineStr"/>
-      <c r="M321" t="inlineStr"/>
       <c r="N321" t="n">
         <v>0</v>
       </c>
@@ -53358,8 +52718,6 @@
       <c r="K322" t="n">
         <v>1</v>
       </c>
-      <c r="L322" t="inlineStr"/>
-      <c r="M322" t="inlineStr"/>
       <c r="N322" t="n">
         <v>0</v>
       </c>
@@ -53410,8 +52768,6 @@
       <c r="K323" t="n">
         <v>1</v>
       </c>
-      <c r="L323" t="inlineStr"/>
-      <c r="M323" t="inlineStr"/>
       <c r="N323" t="n">
         <v>0</v>
       </c>
@@ -53462,8 +52818,6 @@
       <c r="K324" t="n">
         <v>1</v>
       </c>
-      <c r="L324" t="inlineStr"/>
-      <c r="M324" t="inlineStr"/>
       <c r="N324" t="n">
         <v>0</v>
       </c>
@@ -53514,8 +52868,6 @@
       <c r="K325" t="n">
         <v>1</v>
       </c>
-      <c r="L325" t="inlineStr"/>
-      <c r="M325" t="inlineStr"/>
       <c r="N325" t="n">
         <v>0</v>
       </c>
@@ -53566,8 +52918,6 @@
       <c r="K326" t="n">
         <v>1</v>
       </c>
-      <c r="L326" t="inlineStr"/>
-      <c r="M326" t="inlineStr"/>
       <c r="N326" t="n">
         <v>0</v>
       </c>
@@ -53618,8 +52968,6 @@
       <c r="K327" t="n">
         <v>1</v>
       </c>
-      <c r="L327" t="inlineStr"/>
-      <c r="M327" t="inlineStr"/>
       <c r="N327" t="n">
         <v>0</v>
       </c>
@@ -53670,8 +53018,6 @@
       <c r="K328" t="n">
         <v>1</v>
       </c>
-      <c r="L328" t="inlineStr"/>
-      <c r="M328" t="inlineStr"/>
       <c r="N328" t="n">
         <v>0</v>
       </c>
@@ -53722,8 +53068,6 @@
       <c r="K329" t="n">
         <v>1</v>
       </c>
-      <c r="L329" t="inlineStr"/>
-      <c r="M329" t="inlineStr"/>
       <c r="N329" t="n">
         <v>0</v>
       </c>
@@ -53774,8 +53118,6 @@
       <c r="K330" t="n">
         <v>1</v>
       </c>
-      <c r="L330" t="inlineStr"/>
-      <c r="M330" t="inlineStr"/>
       <c r="N330" t="n">
         <v>0</v>
       </c>
@@ -53826,8 +53168,6 @@
       <c r="K331" t="n">
         <v>1</v>
       </c>
-      <c r="L331" t="inlineStr"/>
-      <c r="M331" t="inlineStr"/>
       <c r="N331" t="n">
         <v>0</v>
       </c>
@@ -53878,8 +53218,6 @@
       <c r="K332" t="n">
         <v>1</v>
       </c>
-      <c r="L332" t="inlineStr"/>
-      <c r="M332" t="inlineStr"/>
       <c r="N332" t="n">
         <v>0</v>
       </c>
@@ -53930,8 +53268,6 @@
       <c r="K333" t="n">
         <v>1</v>
       </c>
-      <c r="L333" t="inlineStr"/>
-      <c r="M333" t="inlineStr"/>
       <c r="N333" t="n">
         <v>0</v>
       </c>
@@ -53982,8 +53318,6 @@
       <c r="K334" t="n">
         <v>1</v>
       </c>
-      <c r="L334" t="inlineStr"/>
-      <c r="M334" t="inlineStr"/>
       <c r="N334" t="n">
         <v>0</v>
       </c>
@@ -54034,8 +53368,6 @@
       <c r="K335" t="n">
         <v>1</v>
       </c>
-      <c r="L335" t="inlineStr"/>
-      <c r="M335" t="inlineStr"/>
       <c r="N335" t="n">
         <v>0</v>
       </c>
@@ -54086,8 +53418,6 @@
       <c r="K336" t="n">
         <v>1</v>
       </c>
-      <c r="L336" t="inlineStr"/>
-      <c r="M336" t="inlineStr"/>
       <c r="N336" t="n">
         <v>0</v>
       </c>
@@ -54138,8 +53468,6 @@
       <c r="K337" t="n">
         <v>1</v>
       </c>
-      <c r="L337" t="inlineStr"/>
-      <c r="M337" t="inlineStr"/>
       <c r="N337" t="n">
         <v>0</v>
       </c>
@@ -54190,8 +53518,6 @@
       <c r="K338" t="n">
         <v>1</v>
       </c>
-      <c r="L338" t="inlineStr"/>
-      <c r="M338" t="inlineStr"/>
       <c r="N338" t="n">
         <v>0</v>
       </c>
@@ -54242,8 +53568,6 @@
       <c r="K339" t="n">
         <v>1</v>
       </c>
-      <c r="L339" t="inlineStr"/>
-      <c r="M339" t="inlineStr"/>
       <c r="N339" t="n">
         <v>0</v>
       </c>
@@ -54294,8 +53618,6 @@
       <c r="K340" t="n">
         <v>1</v>
       </c>
-      <c r="L340" t="inlineStr"/>
-      <c r="M340" t="inlineStr"/>
       <c r="N340" t="n">
         <v>0</v>
       </c>
@@ -54346,8 +53668,6 @@
       <c r="K341" t="n">
         <v>1</v>
       </c>
-      <c r="L341" t="inlineStr"/>
-      <c r="M341" t="inlineStr"/>
       <c r="N341" t="n">
         <v>0</v>
       </c>
@@ -54398,8 +53718,6 @@
       <c r="K342" t="n">
         <v>1</v>
       </c>
-      <c r="L342" t="inlineStr"/>
-      <c r="M342" t="inlineStr"/>
       <c r="N342" t="n">
         <v>0</v>
       </c>
@@ -54450,8 +53768,6 @@
       <c r="K343" t="n">
         <v>1</v>
       </c>
-      <c r="L343" t="inlineStr"/>
-      <c r="M343" t="inlineStr"/>
       <c r="N343" t="n">
         <v>0</v>
       </c>
@@ -54502,8 +53818,6 @@
       <c r="K344" t="n">
         <v>1</v>
       </c>
-      <c r="L344" t="inlineStr"/>
-      <c r="M344" t="inlineStr"/>
       <c r="N344" t="n">
         <v>0</v>
       </c>
@@ -54554,8 +53868,6 @@
       <c r="K345" t="n">
         <v>1</v>
       </c>
-      <c r="L345" t="inlineStr"/>
-      <c r="M345" t="inlineStr"/>
       <c r="N345" t="n">
         <v>0</v>
       </c>
@@ -54606,8 +53918,6 @@
       <c r="K346" t="n">
         <v>1</v>
       </c>
-      <c r="L346" t="inlineStr"/>
-      <c r="M346" t="inlineStr"/>
       <c r="N346" t="n">
         <v>0</v>
       </c>
@@ -54658,8 +53968,6 @@
       <c r="K347" t="n">
         <v>1</v>
       </c>
-      <c r="L347" t="inlineStr"/>
-      <c r="M347" t="inlineStr"/>
       <c r="N347" t="n">
         <v>0</v>
       </c>
@@ -54700,8 +54008,6 @@
       <c r="K348" t="n">
         <v>1</v>
       </c>
-      <c r="L348" t="inlineStr"/>
-      <c r="M348" t="inlineStr"/>
       <c r="N348" t="n">
         <v>0</v>
       </c>
@@ -54752,8 +54058,6 @@
       <c r="K349" t="n">
         <v>1</v>
       </c>
-      <c r="L349" t="inlineStr"/>
-      <c r="M349" t="inlineStr"/>
       <c r="N349" t="n">
         <v>0</v>
       </c>
@@ -54804,8 +54108,6 @@
       <c r="K350" t="n">
         <v>1</v>
       </c>
-      <c r="L350" t="inlineStr"/>
-      <c r="M350" t="inlineStr"/>
       <c r="N350" t="n">
         <v>0</v>
       </c>
@@ -54856,8 +54158,6 @@
       <c r="K351" t="n">
         <v>1</v>
       </c>
-      <c r="L351" t="inlineStr"/>
-      <c r="M351" t="inlineStr"/>
       <c r="N351" t="n">
         <v>0</v>
       </c>
@@ -54908,8 +54208,6 @@
       <c r="K352" t="n">
         <v>1</v>
       </c>
-      <c r="L352" t="inlineStr"/>
-      <c r="M352" t="inlineStr"/>
       <c r="N352" t="n">
         <v>0</v>
       </c>
@@ -54950,8 +54248,6 @@
       <c r="K353" t="n">
         <v>1</v>
       </c>
-      <c r="L353" t="inlineStr"/>
-      <c r="M353" t="inlineStr"/>
       <c r="N353" t="n">
         <v>0</v>
       </c>
@@ -54992,8 +54288,6 @@
       <c r="K354" t="n">
         <v>1</v>
       </c>
-      <c r="L354" t="inlineStr"/>
-      <c r="M354" t="inlineStr"/>
       <c r="N354" t="n">
         <v>0</v>
       </c>
@@ -55044,8 +54338,6 @@
       <c r="K355" t="n">
         <v>1</v>
       </c>
-      <c r="L355" t="inlineStr"/>
-      <c r="M355" t="inlineStr"/>
       <c r="N355" t="n">
         <v>0</v>
       </c>
@@ -55086,8 +54378,6 @@
       <c r="K356" t="n">
         <v>1</v>
       </c>
-      <c r="L356" t="inlineStr"/>
-      <c r="M356" t="inlineStr"/>
       <c r="N356" t="n">
         <v>0</v>
       </c>
@@ -55128,8 +54418,6 @@
       <c r="K357" t="n">
         <v>1</v>
       </c>
-      <c r="L357" t="inlineStr"/>
-      <c r="M357" t="inlineStr"/>
       <c r="N357" t="n">
         <v>0</v>
       </c>
@@ -55180,8 +54468,6 @@
       <c r="K358" t="n">
         <v>1</v>
       </c>
-      <c r="L358" t="inlineStr"/>
-      <c r="M358" t="inlineStr"/>
       <c r="N358" t="n">
         <v>0</v>
       </c>
@@ -55232,8 +54518,6 @@
       <c r="K359" t="n">
         <v>1</v>
       </c>
-      <c r="L359" t="inlineStr"/>
-      <c r="M359" t="inlineStr"/>
       <c r="N359" t="n">
         <v>0</v>
       </c>
@@ -55284,8 +54568,6 @@
       <c r="K360" t="n">
         <v>1</v>
       </c>
-      <c r="L360" t="inlineStr"/>
-      <c r="M360" t="inlineStr"/>
       <c r="N360" t="n">
         <v>0</v>
       </c>
@@ -55336,8 +54618,6 @@
       <c r="K361" t="n">
         <v>1</v>
       </c>
-      <c r="L361" t="inlineStr"/>
-      <c r="M361" t="inlineStr"/>
       <c r="N361" t="n">
         <v>0</v>
       </c>
@@ -55388,8 +54668,6 @@
       <c r="K362" t="n">
         <v>1</v>
       </c>
-      <c r="L362" t="inlineStr"/>
-      <c r="M362" t="inlineStr"/>
       <c r="N362" t="n">
         <v>0</v>
       </c>
@@ -55440,8 +54718,6 @@
       <c r="K363" t="n">
         <v>1</v>
       </c>
-      <c r="L363" t="inlineStr"/>
-      <c r="M363" t="inlineStr"/>
       <c r="N363" t="n">
         <v>0</v>
       </c>
@@ -55492,8 +54768,6 @@
       <c r="K364" t="n">
         <v>1</v>
       </c>
-      <c r="L364" t="inlineStr"/>
-      <c r="M364" t="inlineStr"/>
       <c r="N364" t="n">
         <v>0</v>
       </c>
@@ -55544,8 +54818,6 @@
       <c r="K365" t="n">
         <v>1</v>
       </c>
-      <c r="L365" t="inlineStr"/>
-      <c r="M365" t="inlineStr"/>
       <c r="N365" t="n">
         <v>0</v>
       </c>
@@ -55596,8 +54868,6 @@
       <c r="K366" t="n">
         <v>1</v>
       </c>
-      <c r="L366" t="inlineStr"/>
-      <c r="M366" t="inlineStr"/>
       <c r="N366" t="n">
         <v>0</v>
       </c>
@@ -55648,8 +54918,6 @@
       <c r="K367" t="n">
         <v>1</v>
       </c>
-      <c r="L367" t="inlineStr"/>
-      <c r="M367" t="inlineStr"/>
       <c r="N367" t="n">
         <v>0</v>
       </c>
@@ -55680,8 +54948,6 @@
       <c r="K368" t="n">
         <v>1</v>
       </c>
-      <c r="L368" t="inlineStr"/>
-      <c r="M368" t="inlineStr"/>
       <c r="N368" t="n">
         <v>0</v>
       </c>
@@ -55722,8 +54988,6 @@
       <c r="K369" t="n">
         <v>1</v>
       </c>
-      <c r="L369" t="inlineStr"/>
-      <c r="M369" t="inlineStr"/>
       <c r="N369" t="n">
         <v>0</v>
       </c>
@@ -55764,8 +55028,6 @@
       <c r="K370" t="n">
         <v>1</v>
       </c>
-      <c r="L370" t="inlineStr"/>
-      <c r="M370" t="inlineStr"/>
       <c r="N370" t="n">
         <v>0</v>
       </c>
@@ -55816,8 +55078,6 @@
       <c r="K371" t="n">
         <v>1</v>
       </c>
-      <c r="L371" t="inlineStr"/>
-      <c r="M371" t="inlineStr"/>
       <c r="N371" t="n">
         <v>0</v>
       </c>
@@ -55868,8 +55128,6 @@
       <c r="K372" t="n">
         <v>1</v>
       </c>
-      <c r="L372" t="inlineStr"/>
-      <c r="M372" t="inlineStr"/>
       <c r="N372" t="n">
         <v>0</v>
       </c>
@@ -55920,8 +55178,6 @@
       <c r="K373" t="n">
         <v>1</v>
       </c>
-      <c r="L373" t="inlineStr"/>
-      <c r="M373" t="inlineStr"/>
       <c r="N373" t="n">
         <v>0</v>
       </c>
@@ -55962,8 +55218,6 @@
       <c r="K374" t="n">
         <v>1</v>
       </c>
-      <c r="L374" t="inlineStr"/>
-      <c r="M374" t="inlineStr"/>
       <c r="N374" t="n">
         <v>0</v>
       </c>
@@ -56004,8 +55258,6 @@
       <c r="K375" t="n">
         <v>1</v>
       </c>
-      <c r="L375" t="inlineStr"/>
-      <c r="M375" t="inlineStr"/>
       <c r="N375" t="n">
         <v>0</v>
       </c>
@@ -56046,8 +55298,6 @@
       <c r="K376" t="n">
         <v>1</v>
       </c>
-      <c r="L376" t="inlineStr"/>
-      <c r="M376" t="inlineStr"/>
       <c r="N376" t="n">
         <v>0</v>
       </c>
@@ -56098,8 +55348,6 @@
       <c r="K377" t="n">
         <v>1</v>
       </c>
-      <c r="L377" t="inlineStr"/>
-      <c r="M377" t="inlineStr"/>
       <c r="N377" t="n">
         <v>0</v>
       </c>
@@ -56150,8 +55398,6 @@
       <c r="K378" t="n">
         <v>1</v>
       </c>
-      <c r="L378" t="inlineStr"/>
-      <c r="M378" t="inlineStr"/>
       <c r="N378" t="n">
         <v>0</v>
       </c>
@@ -56202,8 +55448,6 @@
       <c r="K379" t="n">
         <v>1</v>
       </c>
-      <c r="L379" t="inlineStr"/>
-      <c r="M379" t="inlineStr"/>
       <c r="N379" t="n">
         <v>0</v>
       </c>
@@ -56254,8 +55498,6 @@
       <c r="K380" t="n">
         <v>1</v>
       </c>
-      <c r="L380" t="inlineStr"/>
-      <c r="M380" t="inlineStr"/>
       <c r="N380" t="n">
         <v>0</v>
       </c>
@@ -56306,8 +55548,6 @@
       <c r="K381" t="n">
         <v>1</v>
       </c>
-      <c r="L381" t="inlineStr"/>
-      <c r="M381" t="inlineStr"/>
       <c r="N381" t="n">
         <v>0</v>
       </c>
@@ -56358,8 +55598,6 @@
       <c r="K382" t="n">
         <v>1</v>
       </c>
-      <c r="L382" t="inlineStr"/>
-      <c r="M382" t="inlineStr"/>
       <c r="N382" t="n">
         <v>0</v>
       </c>
@@ -56410,8 +55648,6 @@
       <c r="K383" t="n">
         <v>1</v>
       </c>
-      <c r="L383" t="inlineStr"/>
-      <c r="M383" t="inlineStr"/>
       <c r="N383" t="n">
         <v>0</v>
       </c>
@@ -56462,8 +55698,6 @@
       <c r="K384" t="n">
         <v>1</v>
       </c>
-      <c r="L384" t="inlineStr"/>
-      <c r="M384" t="inlineStr"/>
       <c r="N384" t="n">
         <v>0</v>
       </c>
@@ -56514,8 +55748,6 @@
       <c r="K385" t="n">
         <v>1</v>
       </c>
-      <c r="L385" t="inlineStr"/>
-      <c r="M385" t="inlineStr"/>
       <c r="N385" t="n">
         <v>0</v>
       </c>
@@ -56566,8 +55798,6 @@
       <c r="K386" t="n">
         <v>1</v>
       </c>
-      <c r="L386" t="inlineStr"/>
-      <c r="M386" t="inlineStr"/>
       <c r="N386" t="n">
         <v>0</v>
       </c>
@@ -56618,8 +55848,6 @@
       <c r="K387" t="n">
         <v>1</v>
       </c>
-      <c r="L387" t="inlineStr"/>
-      <c r="M387" t="inlineStr"/>
       <c r="N387" t="n">
         <v>0</v>
       </c>
@@ -56670,8 +55898,6 @@
       <c r="K388" t="n">
         <v>1</v>
       </c>
-      <c r="L388" t="inlineStr"/>
-      <c r="M388" t="inlineStr"/>
       <c r="N388" t="n">
         <v>0</v>
       </c>
@@ -56722,8 +55948,6 @@
       <c r="K389" t="n">
         <v>1</v>
       </c>
-      <c r="L389" t="inlineStr"/>
-      <c r="M389" t="inlineStr"/>
       <c r="N389" t="n">
         <v>0</v>
       </c>
@@ -56774,8 +55998,6 @@
       <c r="K390" t="n">
         <v>1</v>
       </c>
-      <c r="L390" t="inlineStr"/>
-      <c r="M390" t="inlineStr"/>
       <c r="N390" t="n">
         <v>0</v>
       </c>
@@ -56816,8 +56038,6 @@
       <c r="K391" t="n">
         <v>1</v>
       </c>
-      <c r="L391" t="inlineStr"/>
-      <c r="M391" t="inlineStr"/>
       <c r="N391" t="n">
         <v>0</v>
       </c>
@@ -56868,8 +56088,6 @@
       <c r="K392" t="n">
         <v>1</v>
       </c>
-      <c r="L392" t="inlineStr"/>
-      <c r="M392" t="inlineStr"/>
       <c r="N392" t="n">
         <v>0</v>
       </c>
@@ -56920,8 +56138,6 @@
       <c r="K393" t="n">
         <v>1</v>
       </c>
-      <c r="L393" t="inlineStr"/>
-      <c r="M393" t="inlineStr"/>
       <c r="N393" t="n">
         <v>0</v>
       </c>
@@ -56972,8 +56188,6 @@
       <c r="K394" t="n">
         <v>1</v>
       </c>
-      <c r="L394" t="inlineStr"/>
-      <c r="M394" t="inlineStr"/>
       <c r="N394" t="n">
         <v>0</v>
       </c>
@@ -57024,8 +56238,6 @@
       <c r="K395" t="n">
         <v>1</v>
       </c>
-      <c r="L395" t="inlineStr"/>
-      <c r="M395" t="inlineStr"/>
       <c r="N395" t="n">
         <v>0</v>
       </c>
@@ -57076,8 +56288,6 @@
       <c r="K396" t="n">
         <v>1</v>
       </c>
-      <c r="L396" t="inlineStr"/>
-      <c r="M396" t="inlineStr"/>
       <c r="N396" t="n">
         <v>0</v>
       </c>
@@ -57128,8 +56338,6 @@
       <c r="K397" t="n">
         <v>1</v>
       </c>
-      <c r="L397" t="inlineStr"/>
-      <c r="M397" t="inlineStr"/>
       <c r="N397" t="n">
         <v>0</v>
       </c>
@@ -57180,8 +56388,6 @@
       <c r="K398" t="n">
         <v>1</v>
       </c>
-      <c r="L398" t="inlineStr"/>
-      <c r="M398" t="inlineStr"/>
       <c r="N398" t="n">
         <v>0</v>
       </c>
@@ -57232,8 +56438,6 @@
       <c r="K399" t="n">
         <v>1</v>
       </c>
-      <c r="L399" t="inlineStr"/>
-      <c r="M399" t="inlineStr"/>
       <c r="N399" t="n">
         <v>0</v>
       </c>
@@ -57284,8 +56488,6 @@
       <c r="K400" t="n">
         <v>1</v>
       </c>
-      <c r="L400" t="inlineStr"/>
-      <c r="M400" t="inlineStr"/>
       <c r="N400" t="n">
         <v>0</v>
       </c>
@@ -57336,8 +56538,6 @@
       <c r="K401" t="n">
         <v>1</v>
       </c>
-      <c r="L401" t="inlineStr"/>
-      <c r="M401" t="inlineStr"/>
       <c r="N401" t="n">
         <v>0</v>
       </c>
@@ -57388,8 +56588,6 @@
       <c r="K402" t="n">
         <v>1</v>
       </c>
-      <c r="L402" t="inlineStr"/>
-      <c r="M402" t="inlineStr"/>
       <c r="N402" t="n">
         <v>0</v>
       </c>
@@ -57440,8 +56638,6 @@
       <c r="K403" t="n">
         <v>1</v>
       </c>
-      <c r="L403" t="inlineStr"/>
-      <c r="M403" t="inlineStr"/>
       <c r="N403" t="n">
         <v>0</v>
       </c>
@@ -57492,8 +56688,6 @@
       <c r="K404" t="n">
         <v>1</v>
       </c>
-      <c r="L404" t="inlineStr"/>
-      <c r="M404" t="inlineStr"/>
       <c r="N404" t="n">
         <v>0</v>
       </c>
@@ -57544,8 +56738,6 @@
       <c r="K405" t="n">
         <v>1</v>
       </c>
-      <c r="L405" t="inlineStr"/>
-      <c r="M405" t="inlineStr"/>
       <c r="N405" t="n">
         <v>0</v>
       </c>
@@ -57596,8 +56788,6 @@
       <c r="K406" t="n">
         <v>1</v>
       </c>
-      <c r="L406" t="inlineStr"/>
-      <c r="M406" t="inlineStr"/>
       <c r="N406" t="n">
         <v>0</v>
       </c>
@@ -57648,8 +56838,6 @@
       <c r="K407" t="n">
         <v>1</v>
       </c>
-      <c r="L407" t="inlineStr"/>
-      <c r="M407" t="inlineStr"/>
       <c r="N407" t="n">
         <v>0</v>
       </c>
@@ -57700,8 +56888,6 @@
       <c r="K408" t="n">
         <v>1</v>
       </c>
-      <c r="L408" t="inlineStr"/>
-      <c r="M408" t="inlineStr"/>
       <c r="N408" t="n">
         <v>0</v>
       </c>
@@ -57752,8 +56938,6 @@
       <c r="K409" t="n">
         <v>1</v>
       </c>
-      <c r="L409" t="inlineStr"/>
-      <c r="M409" t="inlineStr"/>
       <c r="N409" t="n">
         <v>0</v>
       </c>
@@ -57804,8 +56988,6 @@
       <c r="K410" t="n">
         <v>1</v>
       </c>
-      <c r="L410" t="inlineStr"/>
-      <c r="M410" t="inlineStr"/>
       <c r="N410" t="n">
         <v>0</v>
       </c>
@@ -57856,8 +57038,6 @@
       <c r="K411" t="n">
         <v>1</v>
       </c>
-      <c r="L411" t="inlineStr"/>
-      <c r="M411" t="inlineStr"/>
       <c r="N411" t="n">
         <v>0</v>
       </c>
@@ -57908,8 +57088,6 @@
       <c r="K412" t="n">
         <v>1</v>
       </c>
-      <c r="L412" t="inlineStr"/>
-      <c r="M412" t="inlineStr"/>
       <c r="N412" t="n">
         <v>0</v>
       </c>
@@ -57960,8 +57138,6 @@
       <c r="K413" t="n">
         <v>1</v>
       </c>
-      <c r="L413" t="inlineStr"/>
-      <c r="M413" t="inlineStr"/>
       <c r="N413" t="n">
         <v>0</v>
       </c>
@@ -58012,8 +57188,6 @@
       <c r="K414" t="n">
         <v>1</v>
       </c>
-      <c r="L414" t="inlineStr"/>
-      <c r="M414" t="inlineStr"/>
       <c r="N414" t="n">
         <v>0</v>
       </c>
@@ -58064,8 +57238,6 @@
       <c r="K415" t="n">
         <v>1</v>
       </c>
-      <c r="L415" t="inlineStr"/>
-      <c r="M415" t="inlineStr"/>
       <c r="N415" t="n">
         <v>0</v>
       </c>
@@ -58116,8 +57288,6 @@
       <c r="K416" t="n">
         <v>1</v>
       </c>
-      <c r="L416" t="inlineStr"/>
-      <c r="M416" t="inlineStr"/>
       <c r="N416" t="n">
         <v>0</v>
       </c>
@@ -58168,8 +57338,6 @@
       <c r="K417" t="n">
         <v>1</v>
       </c>
-      <c r="L417" t="inlineStr"/>
-      <c r="M417" t="inlineStr"/>
       <c r="N417" t="n">
         <v>0</v>
       </c>
@@ -58220,8 +57388,6 @@
       <c r="K418" t="n">
         <v>1</v>
       </c>
-      <c r="L418" t="inlineStr"/>
-      <c r="M418" t="inlineStr"/>
       <c r="N418" t="n">
         <v>0</v>
       </c>
@@ -58262,8 +57428,6 @@
       <c r="K419" t="n">
         <v>1</v>
       </c>
-      <c r="L419" t="inlineStr"/>
-      <c r="M419" t="inlineStr"/>
       <c r="N419" t="n">
         <v>0</v>
       </c>
@@ -58314,8 +57478,6 @@
       <c r="K420" t="n">
         <v>1</v>
       </c>
-      <c r="L420" t="inlineStr"/>
-      <c r="M420" t="inlineStr"/>
       <c r="N420" t="n">
         <v>0</v>
       </c>
@@ -58366,8 +57528,6 @@
       <c r="K421" t="n">
         <v>1</v>
       </c>
-      <c r="L421" t="inlineStr"/>
-      <c r="M421" t="inlineStr"/>
       <c r="N421" t="n">
         <v>0</v>
       </c>
@@ -58418,8 +57578,6 @@
       <c r="K422" t="n">
         <v>1</v>
       </c>
-      <c r="L422" t="inlineStr"/>
-      <c r="M422" t="inlineStr"/>
       <c r="N422" t="n">
         <v>0</v>
       </c>
@@ -58470,8 +57628,6 @@
       <c r="K423" t="n">
         <v>1</v>
       </c>
-      <c r="L423" t="inlineStr"/>
-      <c r="M423" t="inlineStr"/>
       <c r="N423" t="n">
         <v>0</v>
       </c>
@@ -58522,8 +57678,6 @@
       <c r="K424" t="n">
         <v>1</v>
       </c>
-      <c r="L424" t="inlineStr"/>
-      <c r="M424" t="inlineStr"/>
       <c r="N424" t="n">
         <v>0</v>
       </c>
@@ -58574,8 +57728,6 @@
       <c r="K425" t="n">
         <v>1</v>
       </c>
-      <c r="L425" t="inlineStr"/>
-      <c r="M425" t="inlineStr"/>
       <c r="N425" t="n">
         <v>0</v>
       </c>
@@ -58626,8 +57778,6 @@
       <c r="K426" t="n">
         <v>1</v>
       </c>
-      <c r="L426" t="inlineStr"/>
-      <c r="M426" t="inlineStr"/>
       <c r="N426" t="n">
         <v>0</v>
       </c>
@@ -58678,8 +57828,6 @@
       <c r="K427" t="n">
         <v>1</v>
       </c>
-      <c r="L427" t="inlineStr"/>
-      <c r="M427" t="inlineStr"/>
       <c r="N427" t="n">
         <v>0</v>
       </c>
@@ -58730,8 +57878,6 @@
       <c r="K428" t="n">
         <v>1</v>
       </c>
-      <c r="L428" t="inlineStr"/>
-      <c r="M428" t="inlineStr"/>
       <c r="N428" t="n">
         <v>0</v>
       </c>
@@ -58782,8 +57928,6 @@
       <c r="K429" t="n">
         <v>1</v>
       </c>
-      <c r="L429" t="inlineStr"/>
-      <c r="M429" t="inlineStr"/>
       <c r="N429" t="n">
         <v>0</v>
       </c>
@@ -58834,8 +57978,6 @@
       <c r="K430" t="n">
         <v>1</v>
       </c>
-      <c r="L430" t="inlineStr"/>
-      <c r="M430" t="inlineStr"/>
       <c r="N430" t="n">
         <v>0</v>
       </c>
@@ -58866,8 +58008,6 @@
       <c r="K431" t="n">
         <v>1</v>
       </c>
-      <c r="L431" t="inlineStr"/>
-      <c r="M431" t="inlineStr"/>
       <c r="N431" t="n">
         <v>0</v>
       </c>
@@ -58898,8 +58038,6 @@
       <c r="K432" t="n">
         <v>1</v>
       </c>
-      <c r="L432" t="inlineStr"/>
-      <c r="M432" t="inlineStr"/>
       <c r="N432" t="n">
         <v>0</v>
       </c>
@@ -58930,8 +58068,6 @@
       <c r="K433" t="n">
         <v>1</v>
       </c>
-      <c r="L433" t="inlineStr"/>
-      <c r="M433" t="inlineStr"/>
       <c r="N433" t="n">
         <v>0</v>
       </c>
@@ -59084,8 +58220,6 @@
       <c r="K2" t="n">
         <v>0</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -59136,8 +58270,6 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>0</v>
       </c>
@@ -59188,8 +58320,6 @@
       <c r="K4" t="n">
         <v>0</v>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>0</v>
       </c>
@@ -59240,8 +58370,6 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>0</v>
       </c>
@@ -59292,8 +58420,6 @@
       <c r="K6" t="n">
         <v>0</v>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>0</v>
       </c>
@@ -59344,8 +58470,6 @@
       <c r="K7" t="n">
         <v>0</v>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>0</v>
       </c>
@@ -59396,8 +58520,6 @@
       <c r="K8" t="n">
         <v>0</v>
       </c>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>0</v>
       </c>
@@ -59448,8 +58570,6 @@
       <c r="K9" t="n">
         <v>0</v>
       </c>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>0</v>
       </c>
@@ -59500,8 +58620,6 @@
       <c r="K10" t="n">
         <v>0</v>
       </c>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>0</v>
       </c>
@@ -59552,8 +58670,6 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>0</v>
       </c>
@@ -59604,8 +58720,6 @@
       <c r="K12" t="n">
         <v>0</v>
       </c>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>0</v>
       </c>
@@ -59656,8 +58770,6 @@
       <c r="K13" t="n">
         <v>0</v>
       </c>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>0</v>
       </c>
@@ -59708,8 +58820,6 @@
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>0</v>
       </c>
@@ -59750,8 +58860,6 @@
       <c r="K15" t="n">
         <v>0</v>
       </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>0</v>
       </c>
@@ -59802,8 +58910,6 @@
       <c r="K16" t="n">
         <v>0</v>
       </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>0</v>
       </c>
@@ -59854,8 +58960,6 @@
       <c r="K17" t="n">
         <v>0</v>
       </c>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>0</v>
       </c>
@@ -59906,8 +59010,6 @@
       <c r="K18" t="n">
         <v>0</v>
       </c>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>0</v>
       </c>
@@ -59958,8 +59060,6 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>0</v>
       </c>
@@ -60010,8 +59110,6 @@
       <c r="K20" t="n">
         <v>0</v>
       </c>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>0</v>
       </c>
@@ -60062,8 +59160,6 @@
       <c r="K21" t="n">
         <v>0</v>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>0</v>
       </c>
@@ -60114,8 +59210,6 @@
       <c r="K22" t="n">
         <v>0</v>
       </c>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>0</v>
       </c>
@@ -60166,8 +59260,6 @@
       <c r="K23" t="n">
         <v>0</v>
       </c>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>0</v>
       </c>
@@ -60218,8 +59310,6 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>0</v>
       </c>
@@ -60260,8 +59350,6 @@
       <c r="K25" t="n">
         <v>0</v>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
         <v>0</v>
       </c>
@@ -60302,8 +59390,6 @@
       <c r="K26" t="n">
         <v>0</v>
       </c>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
         <v>0</v>
       </c>
@@ -60354,8 +59440,6 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>0</v>
       </c>
@@ -60406,8 +59490,6 @@
       <c r="K28" t="n">
         <v>0</v>
       </c>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>0</v>
       </c>
@@ -60448,8 +59530,6 @@
       <c r="K29" t="n">
         <v>0</v>
       </c>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
         <v>1</v>
       </c>
@@ -60490,8 +59570,6 @@
       <c r="K30" t="n">
         <v>0</v>
       </c>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>1</v>
       </c>
@@ -60532,8 +59610,6 @@
       <c r="K31" t="n">
         <v>0</v>
       </c>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
         <v>1</v>
       </c>
@@ -60574,8 +59650,6 @@
       <c r="K32" t="n">
         <v>0</v>
       </c>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>1</v>
       </c>
@@ -60626,8 +59700,6 @@
       <c r="K33" t="n">
         <v>0</v>
       </c>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
         <v>0</v>
       </c>
@@ -60678,8 +59750,6 @@
       <c r="K34" t="n">
         <v>0</v>
       </c>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>0</v>
       </c>
@@ -60730,8 +59800,6 @@
       <c r="K35" t="n">
         <v>0</v>
       </c>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>0</v>
       </c>
@@ -60772,8 +59840,6 @@
       <c r="K36" t="n">
         <v>0</v>
       </c>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
         <v>0</v>
       </c>
@@ -60814,8 +59880,6 @@
       <c r="K37" t="n">
         <v>0</v>
       </c>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>0</v>
       </c>
@@ -60856,8 +59920,6 @@
       <c r="K38" t="n">
         <v>0</v>
       </c>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>0</v>
       </c>
@@ -60898,8 +59960,6 @@
       <c r="K39" t="n">
         <v>0</v>
       </c>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>0</v>
       </c>
@@ -60950,8 +60010,6 @@
       <c r="K40" t="n">
         <v>0</v>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>0</v>
       </c>
@@ -60992,8 +60050,6 @@
       <c r="K41" t="n">
         <v>0</v>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
         <v>0</v>
       </c>
@@ -61034,8 +60090,6 @@
       <c r="K42" t="n">
         <v>0</v>
       </c>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
         <v>0</v>
       </c>
@@ -61086,8 +60140,6 @@
       <c r="K43" t="n">
         <v>0</v>
       </c>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>1</v>
       </c>
@@ -61138,8 +60190,6 @@
       <c r="K44" t="n">
         <v>0</v>
       </c>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>1</v>
       </c>
@@ -61190,8 +60240,6 @@
       <c r="K45" t="n">
         <v>0</v>
       </c>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
         <v>1</v>
       </c>
@@ -61232,8 +60280,6 @@
       <c r="K46" t="n">
         <v>0</v>
       </c>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>1</v>
       </c>
@@ -61284,8 +60330,6 @@
       <c r="K47" t="n">
         <v>0</v>
       </c>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
         <v>1</v>
       </c>
@@ -61336,8 +60380,6 @@
       <c r="K48" t="n">
         <v>0</v>
       </c>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
         <v>1</v>
       </c>
@@ -61388,8 +60430,6 @@
       <c r="K49" t="n">
         <v>0</v>
       </c>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>0</v>
       </c>
@@ -61440,8 +60480,6 @@
       <c r="K50" t="n">
         <v>0</v>
       </c>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
         <v>0</v>
       </c>
@@ -61492,8 +60530,6 @@
       <c r="K51" t="n">
         <v>0</v>
       </c>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
         <v>0</v>
       </c>
@@ -61544,8 +60580,6 @@
       <c r="K52" t="n">
         <v>0</v>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
         <v>0</v>
       </c>
@@ -61596,8 +60630,6 @@
       <c r="K53" t="n">
         <v>0</v>
       </c>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
         <v>0</v>
       </c>
@@ -61638,8 +60670,6 @@
       <c r="K54" t="n">
         <v>0</v>
       </c>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
         <v>0</v>
       </c>
@@ -61680,8 +60710,6 @@
       <c r="K55" t="n">
         <v>0</v>
       </c>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>0</v>
       </c>
@@ -61722,8 +60750,6 @@
       <c r="K56" t="n">
         <v>0</v>
       </c>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
         <v>0</v>
       </c>
@@ -61774,8 +60800,6 @@
       <c r="K57" t="n">
         <v>0</v>
       </c>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
         <v>0</v>
       </c>
@@ -61826,8 +60850,6 @@
       <c r="K58" t="n">
         <v>0</v>
       </c>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
         <v>0</v>
       </c>
@@ -61868,8 +60890,6 @@
       <c r="K59" t="n">
         <v>0</v>
       </c>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
         <v>0</v>
       </c>
@@ -61920,8 +60940,6 @@
       <c r="K60" t="n">
         <v>0</v>
       </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
         <v>0</v>
       </c>
@@ -61972,8 +60990,6 @@
       <c r="K61" t="n">
         <v>0</v>
       </c>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
         <v>0</v>
       </c>
@@ -62024,8 +61040,6 @@
       <c r="K62" t="n">
         <v>0</v>
       </c>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
         <v>0</v>
       </c>
@@ -62066,8 +61080,6 @@
       <c r="K63" t="n">
         <v>0</v>
       </c>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
         <v>0</v>
       </c>
@@ -62118,8 +61130,6 @@
       <c r="K64" t="n">
         <v>0</v>
       </c>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
         <v>0</v>
       </c>
@@ -62160,8 +61170,6 @@
       <c r="K65" t="n">
         <v>0</v>
       </c>
-      <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
         <v>0</v>
       </c>
@@ -62212,8 +61220,6 @@
       <c r="K66" t="n">
         <v>0</v>
       </c>
-      <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
         <v>0</v>
       </c>
@@ -62264,8 +61270,6 @@
       <c r="K67" t="n">
         <v>0</v>
       </c>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
         <v>0</v>
       </c>
@@ -62316,8 +61320,6 @@
       <c r="K68" t="n">
         <v>0</v>
       </c>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
         <v>0</v>
       </c>
@@ -62368,8 +61370,6 @@
       <c r="K69" t="n">
         <v>0</v>
       </c>
-      <c r="L69" t="inlineStr"/>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
         <v>0</v>
       </c>
@@ -62410,8 +61410,6 @@
       <c r="K70" t="n">
         <v>0</v>
       </c>
-      <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
         <v>0</v>
       </c>
@@ -62452,8 +61450,6 @@
       <c r="K71" t="n">
         <v>0</v>
       </c>
-      <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
         <v>0</v>
       </c>
@@ -62504,8 +61500,6 @@
       <c r="K72" t="n">
         <v>0</v>
       </c>
-      <c r="L72" t="inlineStr"/>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
         <v>0</v>
       </c>
@@ -62536,8 +61530,6 @@
       <c r="K73" t="n">
         <v>0</v>
       </c>
-      <c r="L73" t="inlineStr"/>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
         <v>0</v>
       </c>
@@ -62690,8 +61682,6 @@
       <c r="K2" t="n">
         <v>1</v>
       </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>0</v>
       </c>
@@ -62742,8 +61732,6 @@
       <c r="K3" t="n">
         <v>1</v>
       </c>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>0</v>
       </c>
@@ -64823,7 +63811,6 @@
           <t>2025-11-25 22:36</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
         <v>1</v>
       </c>
@@ -64869,7 +63856,6 @@
           <t>2025-11-30 17:38</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
         <v>1</v>
       </c>
@@ -64925,7 +63911,6 @@
           <t>2025-12-03 21:27</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
         <v>1</v>
       </c>
@@ -64981,7 +63966,6 @@
           <t>2025-12-03 22:08</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
         <v>1</v>
       </c>
@@ -65037,7 +64021,6 @@
           <t>2025-12-03 22:13</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>1</v>
       </c>
@@ -65093,7 +64076,6 @@
           <t>2025-12-24 21:03</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
         <v>1</v>
       </c>
@@ -65149,7 +64131,6 @@
           <t>2025-12-24 21:03</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>1</v>
       </c>
@@ -65205,7 +64186,6 @@
           <t>2025-12-24 21:03</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
         <v>1</v>
       </c>
@@ -65261,7 +64241,6 @@
           <t>2025-12-24 21:03</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>1</v>
       </c>
@@ -65317,7 +64296,6 @@
           <t>2025-12-24 21:03</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
         <v>1</v>
       </c>
@@ -65373,7 +64351,6 @@
           <t>2025-12-29 20:16</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>1</v>
       </c>
@@ -65419,7 +64396,6 @@
           <t>2025-12-29 20:16</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>1</v>
       </c>
@@ -65465,7 +64441,6 @@
           <t>2025-12-29 20:16</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
         <v>1</v>
       </c>
@@ -65511,7 +64486,6 @@
           <t>2025-12-29 20:16</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
         <v>1</v>
       </c>
@@ -65567,7 +64541,6 @@
           <t>2026-01-05 16:16</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
         <v>1</v>
       </c>
@@ -65613,7 +64586,6 @@
           <t>2026-01-28 16:19</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>1</v>
       </c>
@@ -65659,7 +64631,6 @@
           <t>2026-01-28 16:19</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>1</v>
       </c>
@@ -65705,7 +64676,6 @@
           <t>2026-01-28 16:19</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
         <v>1</v>
       </c>
@@ -65751,7 +64721,6 @@
           <t>2026-01-28 16:19</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
         <v>1</v>
       </c>
@@ -65797,7 +64766,6 @@
           <t>2026-01-28 16:19</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>1</v>
       </c>
@@ -65843,7 +64811,6 @@
           <t>2026-01-29 12:40</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>1</v>
       </c>
@@ -65899,7 +64866,6 @@
           <t>2026-03-30 18:58</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>1</v>
       </c>
@@ -65955,7 +64921,6 @@
           <t>2026-01-27 12:58</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>1</v>
       </c>
@@ -66011,7 +64976,6 @@
           <t>2026-01-27 12:58</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
         <v>1</v>
       </c>
@@ -66067,7 +65031,6 @@
           <t>2026-01-28 20:02</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
         <v>1</v>
       </c>
@@ -66123,7 +65086,6 @@
           <t>2026-01-28 20:02</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>1</v>
       </c>
@@ -66179,7 +65141,6 @@
           <t>2026-01-28 20:36</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>1</v>
       </c>
@@ -66235,7 +65196,6 @@
           <t>2026-01-28 20:36</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
         <v>1</v>
       </c>
@@ -66291,7 +65251,6 @@
           <t>2026-02-01 16:31</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>1</v>
       </c>
@@ -66347,7 +65306,6 @@
           <t>2026-02-09 18:51</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
         <v>1</v>
       </c>
@@ -66403,7 +65361,6 @@
           <t>2026-02-09 18:51</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>1</v>
       </c>
@@ -66459,7 +65416,6 @@
           <t>2026-02-09 18:57</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
         <v>1</v>
       </c>
@@ -66495,7 +65451,6 @@
           <t>2026-02-09 18:57</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
         <v>1</v>
       </c>
@@ -66551,7 +65506,6 @@
           <t>2026-02-09 19:25</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
         <v>1</v>
       </c>
@@ -66597,7 +65551,6 @@
           <t>2026-02-18 16:29</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
         <v>1</v>
       </c>
@@ -66653,7 +65606,6 @@
           <t>2026-02-18 16:29</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>1</v>
       </c>
@@ -66709,7 +65661,6 @@
           <t>2026-02-18 19:24</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
         <v>1</v>
       </c>
@@ -66745,7 +65696,6 @@
           <t>2026-02-18 19:24</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
         <v>1</v>
       </c>
@@ -66791,7 +65741,6 @@
           <t>2026-02-19 14:11</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
         <v>1</v>
       </c>
@@ -66837,7 +65786,6 @@
           <t>2026-02-19 14:11</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
         <v>1</v>
       </c>
@@ -66883,7 +65831,6 @@
           <t>2026-02-19 14:11</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
         <v>1</v>
       </c>
@@ -66929,7 +65876,6 @@
           <t>2026-02-19 14:11</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>1</v>
       </c>
@@ -66985,7 +65931,6 @@
           <t>2026-02-19 14:11</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>1</v>
       </c>
@@ -67041,7 +65986,6 @@
           <t>2026-02-22 15:14</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
         <v>1</v>
       </c>
@@ -67097,7 +66041,6 @@
           <t>2026-02-19 15:44</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>1</v>
       </c>
@@ -67153,7 +66096,6 @@
           <t>2026-02-20 21:00</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
         <v>1</v>
       </c>
@@ -67209,7 +66151,6 @@
           <t>2026-02-21 12:25</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
         <v>1</v>
       </c>
@@ -67265,7 +66206,6 @@
           <t>2026-02-24 14:22</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>1</v>
       </c>
@@ -67321,7 +66261,6 @@
           <t>2026-03-05 16:00</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
         <v>1</v>
       </c>
@@ -67377,7 +66316,6 @@
           <t>2026-03-07 16:09</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
         <v>1</v>
       </c>
@@ -67423,7 +66361,6 @@
           <t>2026-03-08 16:56</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
         <v>1</v>
       </c>
@@ -67469,7 +66406,6 @@
           <t>2026-03-08 16:56</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
         <v>1</v>
       </c>
@@ -67525,7 +66461,6 @@
           <t>2026-03-13 10:36</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
         <v>1</v>
       </c>
@@ -67581,7 +66516,6 @@
           <t>2026-03-13 16:36</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>1</v>
       </c>
@@ -67637,7 +66571,6 @@
           <t>2026-03-15 16:49</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
         <v>1</v>
       </c>
@@ -67693,7 +66626,6 @@
           <t>2026-03-28 20:50</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
         <v>1</v>
       </c>
@@ -67749,7 +66681,6 @@
           <t>2026-04-06 10:58</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
         <v>1</v>
       </c>
@@ -67805,7 +66736,6 @@
           <t>2026-04-06 16:06</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
         <v>1</v>
       </c>
@@ -67821,7 +66751,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N195"/>
+  <dimension ref="A1:T195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -67911,6 +66841,36 @@
           <t>_非微信非支付宝笔数</t>
         </is>
       </c>
+      <c r="O1" s="7" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="P1" s="7" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q1" s="7" t="inlineStr">
+        <is>
+          <t>减免</t>
+        </is>
+      </c>
+      <c r="R1" s="7" t="inlineStr">
+        <is>
+          <t>免除</t>
+        </is>
+      </c>
+      <c r="S1" s="7" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T1" s="7" t="inlineStr">
+        <is>
+          <t>减免2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -67963,8 +66923,23 @@
           <t>2025-10-30 18:15</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q2" t="n">
+        <v>0</v>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68019,8 +66994,18 @@
           <t>2025-11-04 21:04</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0</v>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68075,8 +67060,23 @@
           <t>2025-10-30 18:45</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68131,8 +67131,23 @@
           <t>2025-10-30 23:54</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68187,9 +67202,19 @@
           <t>2025-10-30 23:54</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="n">
         <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>279.99</v>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T6" t="n">
+        <v>279.99</v>
       </c>
     </row>
     <row r="7">
@@ -68243,8 +67268,23 @@
           <t>2025-11-01 01:03</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68299,9 +67339,19 @@
           <t>2025-11-01 13:53</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="n">
         <v>0</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>319.99</v>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T8" t="n">
+        <v>319.99</v>
       </c>
     </row>
     <row r="9">
@@ -68355,8 +67405,23 @@
           <t>2025-11-01 13:53</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68411,9 +67476,19 @@
           <t>2025-11-01 13:53</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="n">
         <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T10" t="n">
+        <v>39.99</v>
       </c>
     </row>
     <row r="11">
@@ -68467,8 +67542,23 @@
           <t>2025-11-01 21:52</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68523,9 +67613,19 @@
           <t>2025-11-03 08:35</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="n">
         <v>0</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>399.99</v>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T12" t="n">
+        <v>399.99</v>
       </c>
     </row>
     <row r="13">
@@ -68579,9 +67679,19 @@
           <t>2025-11-03 07:25</t>
         </is>
       </c>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="n">
         <v>0</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T13" t="n">
+        <v>299.99</v>
       </c>
     </row>
     <row r="14">
@@ -68635,8 +67745,23 @@
           <t>2025-11-04 15:46</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68681,8 +67806,18 @@
           <t>2025-11-11 14:04</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68737,8 +67872,18 @@
           <t>2025-11-11 14:04</t>
         </is>
       </c>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68793,9 +67938,19 @@
           <t>2025-11-05 20:30</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="n">
         <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T17" t="n">
+        <v>149.99</v>
       </c>
     </row>
     <row r="18">
@@ -68849,9 +68004,19 @@
           <t>2025-11-05 20:38</t>
         </is>
       </c>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="n">
         <v>0</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>149.99</v>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T18" t="n">
+        <v>149.99</v>
       </c>
     </row>
     <row r="19">
@@ -68905,8 +68070,23 @@
           <t>2025-11-05 22:02</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -68961,8 +68141,23 @@
           <t>2025-11-07 15:43</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69017,9 +68212,19 @@
           <t>2025-11-07 22:07</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="n">
         <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>39.99</v>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T21" t="n">
+        <v>39.99</v>
       </c>
     </row>
     <row r="22">
@@ -69073,9 +68278,19 @@
           <t>2025-11-08 12:28</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="n">
         <v>0</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>49.99</v>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T22" t="n">
+        <v>49.99</v>
       </c>
     </row>
     <row r="23">
@@ -69129,9 +68344,19 @@
           <t>2025-11-08 12:28</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="n">
         <v>0</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T23" t="n">
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="24">
@@ -69185,9 +68410,19 @@
           <t>2025-11-08 12:27</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="n">
         <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>69.98999999999999</v>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T24" t="n">
+        <v>69.98999999999999</v>
       </c>
     </row>
     <row r="25">
@@ -69241,8 +68476,18 @@
           <t>2025-11-14 16:26</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69297,8 +68542,18 @@
           <t>2025-12-04 09:09</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr"/>
       <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69353,9 +68608,14 @@
           <t>2025-11-22 12:15</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr"/>
       <c r="N27" t="n">
         <v>0</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>90</v>
+      </c>
+      <c r="T27" t="n">
+        <v>90</v>
       </c>
     </row>
     <row r="28">
@@ -69409,9 +68669,14 @@
           <t>2025-11-22 15:47</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr"/>
       <c r="N28" t="n">
         <v>0</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>50</v>
+      </c>
+      <c r="T28" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="29">
@@ -69465,9 +68730,14 @@
           <t>2025-11-23 15:03</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr"/>
       <c r="N29" t="n">
         <v>0</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>50</v>
+      </c>
+      <c r="T29" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="30">
@@ -69521,9 +68791,14 @@
           <t>2025-11-23 15:03</t>
         </is>
       </c>
-      <c r="M30" t="inlineStr"/>
       <c r="N30" t="n">
         <v>0</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>50</v>
+      </c>
+      <c r="T30" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="31">
@@ -69577,9 +68852,14 @@
           <t>2025-11-23 15:03</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr"/>
       <c r="N31" t="n">
         <v>0</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>50</v>
+      </c>
+      <c r="T31" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="32">
@@ -69633,9 +68913,14 @@
           <t>2025-11-23 15:47</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr"/>
       <c r="N32" t="n">
         <v>0</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>50</v>
+      </c>
+      <c r="T32" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="33">
@@ -69679,8 +68964,18 @@
           <t>2025-11-25 16:38</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr"/>
       <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>0</v>
+      </c>
+      <c r="R33" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T33" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69735,8 +69030,23 @@
           <t>2025-11-25 22:40</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr"/>
       <c r="N34" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>0</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T34" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69791,8 +69101,23 @@
           <t>2025-11-26 11:18</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr"/>
       <c r="N35" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>0</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T35" t="n">
         <v>0</v>
       </c>
     </row>
@@ -69847,9 +69172,19 @@
           <t>2025-11-26 21:26</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr"/>
       <c r="N36" t="n">
         <v>0</v>
+      </c>
+      <c r="Q36" t="n">
+        <v>259.96</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T36" t="n">
+        <v>259.96</v>
       </c>
     </row>
     <row r="37">
@@ -69903,9 +69238,14 @@
           <t>2025-11-27 16:38</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr"/>
       <c r="N37" t="n">
         <v>0</v>
+      </c>
+      <c r="Q37" t="n">
+        <v>50</v>
+      </c>
+      <c r="T37" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="38">
@@ -69959,8 +69299,18 @@
           <t>2025-11-29 12:19</t>
         </is>
       </c>
-      <c r="M38" t="inlineStr"/>
       <c r="N38" t="n">
+        <v>0</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70015,8 +69365,18 @@
           <t>2025-11-29 12:19</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr"/>
       <c r="N39" t="n">
+        <v>0</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70071,8 +69431,18 @@
           <t>2025-11-29 14:39</t>
         </is>
       </c>
-      <c r="M40" t="inlineStr"/>
       <c r="N40" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70127,8 +69497,18 @@
           <t>2025-11-29 14:39</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70183,9 +69563,19 @@
           <t>2025-11-27 23:10</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
         <v>0</v>
+      </c>
+      <c r="Q42" t="n">
+        <v>259.96</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T42" t="n">
+        <v>259.96</v>
       </c>
     </row>
     <row r="43">
@@ -70239,9 +69629,19 @@
           <t>2025-11-28 14:29</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr"/>
       <c r="N43" t="n">
         <v>0</v>
+      </c>
+      <c r="Q43" t="n">
+        <v>259.98</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T43" t="n">
+        <v>259.98</v>
       </c>
     </row>
     <row r="44">
@@ -70295,9 +69695,19 @@
           <t>2025-11-28 22:01</t>
         </is>
       </c>
-      <c r="M44" t="inlineStr"/>
       <c r="N44" t="n">
         <v>0</v>
+      </c>
+      <c r="Q44" t="n">
+        <v>259.98</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T44" t="n">
+        <v>259.98</v>
       </c>
     </row>
     <row r="45">
@@ -70351,8 +69761,23 @@
           <t>2025-11-28 22:45</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr"/>
       <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>0</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T45" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70407,9 +69832,14 @@
           <t>2025-11-29 21:55</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr"/>
       <c r="N46" t="n">
         <v>0</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>80</v>
+      </c>
+      <c r="T46" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="47">
@@ -70453,8 +69883,18 @@
           <t>2025-12-01 16:11</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr"/>
       <c r="N47" t="n">
+        <v>0</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70499,8 +69939,18 @@
           <t>2025-12-01 16:11</t>
         </is>
       </c>
-      <c r="M48" t="inlineStr"/>
       <c r="N48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70555,9 +70005,19 @@
           <t>2025-11-30 20:01</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr"/>
       <c r="N49" t="n">
         <v>0</v>
+      </c>
+      <c r="Q49" t="n">
+        <v>259.98</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T49" t="n">
+        <v>259.98</v>
       </c>
     </row>
     <row r="50">
@@ -70601,8 +70061,18 @@
           <t>2025-12-01 13:22</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr"/>
       <c r="N50" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="n">
+        <v>0</v>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T50" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70657,8 +70127,18 @@
           <t>2025-12-01 10:25</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr"/>
       <c r="N51" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="n">
+        <v>0</v>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T51" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70713,8 +70193,18 @@
           <t>2025-12-03 17:00</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr"/>
       <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70769,9 +70259,19 @@
           <t>2025-12-03 22:05</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr"/>
       <c r="N53" t="n">
         <v>0</v>
+      </c>
+      <c r="Q53" t="n">
+        <v>259.99</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T53" t="n">
+        <v>259.99</v>
       </c>
     </row>
     <row r="54">
@@ -70825,9 +70325,14 @@
           <t>2025-12-04 16:28</t>
         </is>
       </c>
-      <c r="M54" t="inlineStr"/>
       <c r="N54" t="n">
         <v>0</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>50</v>
+      </c>
+      <c r="T54" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="55">
@@ -70881,9 +70386,14 @@
           <t>2025-12-08 21:23</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr"/>
       <c r="N55" t="n">
         <v>0</v>
+      </c>
+      <c r="Q55" t="n">
+        <v>299.99</v>
+      </c>
+      <c r="T55" t="n">
+        <v>299.99</v>
       </c>
     </row>
     <row r="56">
@@ -70937,8 +70447,13 @@
           <t>2025-12-05 12:52</t>
         </is>
       </c>
-      <c r="M56" t="inlineStr"/>
       <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
         <v>0</v>
       </c>
     </row>
@@ -70993,9 +70508,14 @@
           <t>2025-12-07 13:12</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr"/>
       <c r="N57" t="n">
         <v>0</v>
+      </c>
+      <c r="Q57" t="n">
+        <v>50</v>
+      </c>
+      <c r="T57" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="58">
@@ -71049,9 +70569,14 @@
           <t>2025-12-08 15:08</t>
         </is>
       </c>
-      <c r="M58" t="inlineStr"/>
       <c r="N58" t="n">
         <v>0</v>
+      </c>
+      <c r="Q58" t="n">
+        <v>50</v>
+      </c>
+      <c r="T58" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="59">
@@ -71095,8 +70620,18 @@
           <t>2025-12-14 19:25</t>
         </is>
       </c>
-      <c r="M59" t="inlineStr"/>
       <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71151,9 +70686,14 @@
           <t>2025-12-13 16:31</t>
         </is>
       </c>
-      <c r="M60" t="inlineStr"/>
       <c r="N60" t="n">
         <v>0</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>50</v>
+      </c>
+      <c r="T60" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="61">
@@ -71197,8 +70737,18 @@
           <t>2025-12-13 19:28</t>
         </is>
       </c>
-      <c r="M61" t="inlineStr"/>
       <c r="N61" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q61" t="n">
+        <v>0</v>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T61" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71243,8 +70793,18 @@
           <t>2025-12-14 09:55</t>
         </is>
       </c>
-      <c r="M62" t="inlineStr"/>
       <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71299,9 +70859,14 @@
           <t>2025-12-14 16:43</t>
         </is>
       </c>
-      <c r="M63" t="inlineStr"/>
       <c r="N63" t="n">
         <v>0</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>50</v>
+      </c>
+      <c r="T63" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="64">
@@ -71345,8 +70910,18 @@
           <t>2025-12-15 11:34</t>
         </is>
       </c>
-      <c r="M64" t="inlineStr"/>
       <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T64" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71391,8 +70966,18 @@
           <t>2025-12-20 15:01</t>
         </is>
       </c>
-      <c r="M65" t="inlineStr"/>
       <c r="N65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71437,8 +71022,18 @@
           <t>2025-12-20 15:01</t>
         </is>
       </c>
-      <c r="M66" t="inlineStr"/>
       <c r="N66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71483,8 +71078,18 @@
           <t>2025-12-20 15:01</t>
         </is>
       </c>
-      <c r="M67" t="inlineStr"/>
       <c r="N67" t="n">
+        <v>0</v>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71539,9 +71144,14 @@
           <t>2025-12-21 15:03</t>
         </is>
       </c>
-      <c r="M68" t="inlineStr"/>
       <c r="N68" t="n">
         <v>0</v>
+      </c>
+      <c r="Q68" t="n">
+        <v>80</v>
+      </c>
+      <c r="T68" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="69">
@@ -71585,8 +71195,18 @@
           <t>2025-12-21 16:14</t>
         </is>
       </c>
-      <c r="M69" t="inlineStr"/>
       <c r="N69" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q69" t="n">
+        <v>0</v>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T69" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71631,8 +71251,18 @@
           <t>2025-12-24 13:30</t>
         </is>
       </c>
-      <c r="M70" t="inlineStr"/>
       <c r="N70" t="n">
+        <v>0</v>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71677,8 +71307,18 @@
           <t>2025-12-24 13:30</t>
         </is>
       </c>
-      <c r="M71" t="inlineStr"/>
       <c r="N71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71733,8 +71373,18 @@
           <t>2025-12-24 13:30</t>
         </is>
       </c>
-      <c r="M72" t="inlineStr"/>
       <c r="N72" t="n">
+        <v>0</v>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71789,8 +71439,18 @@
           <t>2025-12-24 13:30</t>
         </is>
       </c>
-      <c r="M73" t="inlineStr"/>
       <c r="N73" t="n">
+        <v>0</v>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>0</v>
+      </c>
+      <c r="T73" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71835,8 +71495,18 @@
           <t>2025-12-22 14:20</t>
         </is>
       </c>
-      <c r="M74" t="inlineStr"/>
       <c r="N74" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q74" t="n">
+        <v>0</v>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T74" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71881,8 +71551,18 @@
           <t>2025-12-22 14:20</t>
         </is>
       </c>
-      <c r="M75" t="inlineStr"/>
       <c r="N75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T75" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71927,8 +71607,18 @@
           <t>2025-12-31 12:56</t>
         </is>
       </c>
-      <c r="M76" t="inlineStr"/>
       <c r="N76" t="n">
+        <v>0</v>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
         <v>0</v>
       </c>
     </row>
@@ -71983,8 +71673,18 @@
           <t>2025-12-24 13:12</t>
         </is>
       </c>
-      <c r="M77" t="inlineStr"/>
       <c r="N77" t="n">
+        <v>0</v>
+      </c>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72039,8 +71739,18 @@
           <t>2025-12-31 12:06</t>
         </is>
       </c>
-      <c r="M78" t="inlineStr"/>
       <c r="N78" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q78" t="n">
+        <v>0</v>
+      </c>
+      <c r="R78" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T78" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72095,8 +71805,18 @@
           <t>2025-12-31 11:58</t>
         </is>
       </c>
-      <c r="M79" t="inlineStr"/>
       <c r="N79" t="n">
+        <v>0</v>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>0</v>
+      </c>
+      <c r="T79" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72151,8 +71871,18 @@
           <t>2025-12-31 11:58</t>
         </is>
       </c>
-      <c r="M80" t="inlineStr"/>
       <c r="N80" t="n">
+        <v>0</v>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72197,8 +71927,18 @@
           <t>2025-12-30 16:48</t>
         </is>
       </c>
-      <c r="M81" t="inlineStr"/>
       <c r="N81" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q81" t="n">
+        <v>0</v>
+      </c>
+      <c r="R81" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T81" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72253,9 +71993,14 @@
           <t>2025-12-25 16:47</t>
         </is>
       </c>
-      <c r="M82" t="inlineStr"/>
       <c r="N82" t="n">
         <v>0</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>50</v>
+      </c>
+      <c r="T82" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="83">
@@ -72309,9 +72054,14 @@
           <t>2025-12-26 12:25</t>
         </is>
       </c>
-      <c r="M83" t="inlineStr"/>
       <c r="N83" t="n">
         <v>0</v>
+      </c>
+      <c r="Q83" t="n">
+        <v>80</v>
+      </c>
+      <c r="T83" t="n">
+        <v>80</v>
       </c>
     </row>
     <row r="84">
@@ -72355,8 +72105,18 @@
           <t>2025-12-26 18:25</t>
         </is>
       </c>
-      <c r="M84" t="inlineStr"/>
       <c r="N84" t="n">
+        <v>0</v>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>0</v>
+      </c>
+      <c r="T84" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72401,8 +72161,18 @@
           <t>2025-12-29 14:41</t>
         </is>
       </c>
-      <c r="M85" t="inlineStr"/>
       <c r="N85" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>0</v>
+      </c>
+      <c r="R85" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T85" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72457,8 +72227,18 @@
           <t>2025-12-28 12:25</t>
         </is>
       </c>
-      <c r="M86" t="inlineStr"/>
       <c r="N86" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>0</v>
+      </c>
+      <c r="R86" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T86" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72503,8 +72283,18 @@
           <t>2025-12-27 16:35</t>
         </is>
       </c>
-      <c r="M87" t="inlineStr"/>
       <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72549,8 +72339,18 @@
           <t>2025-12-28 09:19</t>
         </is>
       </c>
-      <c r="M88" t="inlineStr"/>
       <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>0</v>
+      </c>
+      <c r="R88" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T88" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72605,9 +72405,14 @@
           <t>2025-12-28 16:07</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr"/>
       <c r="N89" t="n">
         <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>50</v>
+      </c>
+      <c r="T89" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="90">
@@ -72661,9 +72466,19 @@
           <t>2025-12-28 22:21</t>
         </is>
       </c>
-      <c r="M90" t="inlineStr"/>
       <c r="N90" t="n">
         <v>0</v>
+      </c>
+      <c r="Q90" t="n">
+        <v>259.99</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>测试</t>
+        </is>
+      </c>
+      <c r="T90" t="n">
+        <v>259.99</v>
       </c>
     </row>
     <row r="91">
@@ -72717,8 +72532,13 @@
           <t>2025-12-30 16:40</t>
         </is>
       </c>
-      <c r="M91" t="inlineStr"/>
       <c r="N91" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q91" t="n">
+        <v>0</v>
+      </c>
+      <c r="T91" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72773,8 +72593,18 @@
           <t>2026-01-03 12:17</t>
         </is>
       </c>
-      <c r="M92" t="inlineStr"/>
       <c r="N92" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q92" t="n">
+        <v>0</v>
+      </c>
+      <c r="R92" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T92" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72819,9 +72649,14 @@
           <t>2026-01-02 12:59</t>
         </is>
       </c>
-      <c r="M93" t="inlineStr"/>
       <c r="N93" t="n">
         <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>120</v>
+      </c>
+      <c r="T93" t="n">
+        <v>120</v>
       </c>
     </row>
     <row r="94">
@@ -72865,8 +72700,18 @@
           <t>2026-01-02 16:41</t>
         </is>
       </c>
-      <c r="M94" t="inlineStr"/>
       <c r="N94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>0</v>
+      </c>
+      <c r="T94" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72911,8 +72756,18 @@
           <t>2026-01-03 08:54</t>
         </is>
       </c>
-      <c r="M95" t="inlineStr"/>
       <c r="N95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>0</v>
+      </c>
+      <c r="R95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T95" t="n">
         <v>0</v>
       </c>
     </row>
@@ -72957,8 +72812,13 @@
           <t>2026-01-03 16:21</t>
         </is>
       </c>
-      <c r="M96" t="inlineStr"/>
       <c r="N96" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q96" t="n">
+        <v>0</v>
+      </c>
+      <c r="T96" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73013,8 +72873,18 @@
           <t>2026-01-05 14:23</t>
         </is>
       </c>
-      <c r="M97" t="inlineStr"/>
       <c r="N97" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q97" t="n">
+        <v>0</v>
+      </c>
+      <c r="R97" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T97" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73069,8 +72939,18 @@
           <t>2026-01-08 16:50</t>
         </is>
       </c>
-      <c r="M98" t="inlineStr"/>
       <c r="N98" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q98" t="n">
+        <v>0</v>
+      </c>
+      <c r="R98" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T98" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73125,8 +73005,18 @@
           <t>2026-01-08 16:50</t>
         </is>
       </c>
-      <c r="M99" t="inlineStr"/>
       <c r="N99" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q99" t="n">
+        <v>0</v>
+      </c>
+      <c r="R99" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T99" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73171,9 +73061,14 @@
           <t>2026-01-11 09:50</t>
         </is>
       </c>
-      <c r="M100" t="inlineStr"/>
       <c r="N100" t="n">
         <v>0</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>260</v>
+      </c>
+      <c r="T100" t="n">
+        <v>260</v>
       </c>
     </row>
     <row r="101">
@@ -73217,8 +73112,18 @@
           <t>2026-01-12 12:38</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr"/>
       <c r="N101" t="n">
+        <v>0</v>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>0</v>
+      </c>
+      <c r="T101" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73263,8 +73168,18 @@
           <t>2026-01-16 10:01</t>
         </is>
       </c>
-      <c r="M102" t="inlineStr"/>
       <c r="N102" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>0</v>
+      </c>
+      <c r="T102" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73309,8 +73224,18 @@
           <t>2026-01-17 16:16</t>
         </is>
       </c>
-      <c r="M103" t="inlineStr"/>
       <c r="N103" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q103" t="n">
+        <v>0</v>
+      </c>
+      <c r="R103" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T103" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73355,8 +73280,18 @@
           <t>2026-01-17 18:32</t>
         </is>
       </c>
-      <c r="M104" t="inlineStr"/>
       <c r="N104" t="n">
+        <v>0</v>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>0</v>
+      </c>
+      <c r="T104" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73401,8 +73336,23 @@
           <t>2026-01-17 20:39</t>
         </is>
       </c>
-      <c r="M105" t="inlineStr"/>
       <c r="N105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>0</v>
+      </c>
+      <c r="R105" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T105" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73457,8 +73407,18 @@
           <t>2026-01-18 16:25</t>
         </is>
       </c>
-      <c r="M106" t="inlineStr"/>
       <c r="N106" t="n">
+        <v>0</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>0</v>
+      </c>
+      <c r="T106" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73513,8 +73473,18 @@
           <t>2026-01-18 16:23</t>
         </is>
       </c>
-      <c r="M107" t="inlineStr"/>
       <c r="N107" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73569,8 +73539,18 @@
           <t>2026-01-23 19:07</t>
         </is>
       </c>
-      <c r="M108" t="inlineStr"/>
       <c r="N108" t="n">
+        <v>0</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q108" t="n">
+        <v>0</v>
+      </c>
+      <c r="T108" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73625,8 +73605,18 @@
           <t>2026-01-30 16:26</t>
         </is>
       </c>
-      <c r="M109" t="inlineStr"/>
       <c r="N109" t="n">
+        <v>0</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q109" t="n">
+        <v>0</v>
+      </c>
+      <c r="T109" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73671,8 +73661,18 @@
           <t>2026-01-26 14:17</t>
         </is>
       </c>
-      <c r="M110" t="inlineStr"/>
       <c r="N110" t="n">
+        <v>0</v>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>0</v>
+      </c>
+      <c r="T110" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73727,9 +73727,14 @@
           <t>2026-01-25 13:37</t>
         </is>
       </c>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="n">
         <v>0</v>
+      </c>
+      <c r="Q111" t="n">
+        <v>50</v>
+      </c>
+      <c r="T111" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="112">
@@ -73773,8 +73778,18 @@
           <t>2026-01-24 12:07</t>
         </is>
       </c>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="n">
+        <v>0</v>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>0</v>
+      </c>
+      <c r="T112" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73829,9 +73844,14 @@
           <t>2026-01-24 16:14</t>
         </is>
       </c>
-      <c r="M113" t="inlineStr"/>
       <c r="N113" t="n">
         <v>0</v>
+      </c>
+      <c r="Q113" t="n">
+        <v>50</v>
+      </c>
+      <c r="T113" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="114">
@@ -73875,8 +73895,18 @@
           <t>2026-01-25 13:22</t>
         </is>
       </c>
-      <c r="M114" t="inlineStr"/>
       <c r="N114" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q114" t="n">
+        <v>0</v>
+      </c>
+      <c r="R114" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T114" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73921,8 +73951,18 @@
           <t>2026-01-24 16:59</t>
         </is>
       </c>
-      <c r="M115" t="inlineStr"/>
       <c r="N115" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q115" t="n">
+        <v>0</v>
+      </c>
+      <c r="R115" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T115" t="n">
         <v>0</v>
       </c>
     </row>
@@ -73977,9 +74017,14 @@
           <t>2026-01-25 15:51</t>
         </is>
       </c>
-      <c r="M116" t="inlineStr"/>
       <c r="N116" t="n">
         <v>0</v>
+      </c>
+      <c r="Q116" t="n">
+        <v>60</v>
+      </c>
+      <c r="T116" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="117">
@@ -74033,9 +74078,14 @@
           <t>2026-01-25 15:51</t>
         </is>
       </c>
-      <c r="M117" t="inlineStr"/>
       <c r="N117" t="n">
         <v>0</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>60</v>
+      </c>
+      <c r="T117" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="118">
@@ -74089,9 +74139,14 @@
           <t>2026-01-25 15:51</t>
         </is>
       </c>
-      <c r="M118" t="inlineStr"/>
       <c r="N118" t="n">
         <v>0</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>60</v>
+      </c>
+      <c r="T118" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="119">
@@ -74145,9 +74200,14 @@
           <t>2026-01-25 15:51</t>
         </is>
       </c>
-      <c r="M119" t="inlineStr"/>
       <c r="N119" t="n">
         <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>60</v>
+      </c>
+      <c r="T119" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="120">
@@ -74201,9 +74261,14 @@
           <t>2026-01-25 14:09</t>
         </is>
       </c>
-      <c r="M120" t="inlineStr"/>
       <c r="N120" t="n">
         <v>0</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>60</v>
+      </c>
+      <c r="T120" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="121">
@@ -74257,9 +74322,14 @@
           <t>2026-01-25 14:09</t>
         </is>
       </c>
-      <c r="M121" t="inlineStr"/>
       <c r="N121" t="n">
         <v>0</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>60</v>
+      </c>
+      <c r="T121" t="n">
+        <v>60</v>
       </c>
     </row>
     <row r="122">
@@ -74313,9 +74383,14 @@
           <t>2026-01-25 17:04</t>
         </is>
       </c>
-      <c r="M122" t="inlineStr"/>
       <c r="N122" t="n">
         <v>0</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>50</v>
+      </c>
+      <c r="T122" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="123">
@@ -74369,9 +74444,14 @@
           <t>2026-01-25 17:04</t>
         </is>
       </c>
-      <c r="M123" t="inlineStr"/>
       <c r="N123" t="n">
         <v>0</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>50</v>
+      </c>
+      <c r="T123" t="n">
+        <v>50</v>
       </c>
     </row>
     <row r="124">
@@ -74425,8 +74505,18 @@
           <t>2026-01-29 10:43</t>
         </is>
       </c>
-      <c r="M124" t="inlineStr"/>
       <c r="N124" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0</v>
+      </c>
+      <c r="R124" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T124" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74471,8 +74561,18 @@
           <t>2026-01-30 22:18</t>
         </is>
       </c>
-      <c r="M125" t="inlineStr"/>
       <c r="N125" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0</v>
+      </c>
+      <c r="R125" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T125" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74517,8 +74617,18 @@
           <t>2026-01-31 15:29</t>
         </is>
       </c>
-      <c r="M126" t="inlineStr"/>
       <c r="N126" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0</v>
+      </c>
+      <c r="R126" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T126" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74573,8 +74683,18 @@
           <t>2026-01-31 18:36</t>
         </is>
       </c>
-      <c r="M127" t="inlineStr"/>
       <c r="N127" t="n">
+        <v>0</v>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74629,8 +74749,18 @@
           <t>2026-02-01 15:22</t>
         </is>
       </c>
-      <c r="M128" t="inlineStr"/>
       <c r="N128" t="n">
+        <v>0</v>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74685,8 +74815,18 @@
           <t>2026-02-01 21:38</t>
         </is>
       </c>
-      <c r="M129" t="inlineStr"/>
       <c r="N129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0</v>
+      </c>
+      <c r="R129" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T129" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74731,8 +74871,18 @@
           <t>2026-02-06 13:24</t>
         </is>
       </c>
-      <c r="M130" t="inlineStr"/>
       <c r="N130" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0</v>
+      </c>
+      <c r="R130" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T130" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74787,8 +74937,18 @@
           <t>2026-02-03 14:44</t>
         </is>
       </c>
-      <c r="M131" t="inlineStr"/>
       <c r="N131" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0</v>
+      </c>
+      <c r="R131" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T131" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74843,8 +75003,18 @@
           <t>2026-02-05 14:43</t>
         </is>
       </c>
-      <c r="M132" t="inlineStr"/>
       <c r="N132" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0</v>
+      </c>
+      <c r="R132" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T132" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74889,8 +75059,18 @@
           <t>2026-02-05 17:01</t>
         </is>
       </c>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="n">
+        <v>0</v>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q133" t="n">
+        <v>0</v>
+      </c>
+      <c r="T133" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74935,8 +75115,18 @@
           <t>2026-02-05 17:01</t>
         </is>
       </c>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="n">
+        <v>0</v>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
         <v>0</v>
       </c>
     </row>
@@ -74981,8 +75171,18 @@
           <t>2026-02-06 11:50</t>
         </is>
       </c>
-      <c r="M135" t="inlineStr"/>
       <c r="N135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T135" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75037,8 +75237,18 @@
           <t>2026-02-06 17:05</t>
         </is>
       </c>
-      <c r="M136" t="inlineStr"/>
       <c r="N136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T136" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75083,8 +75293,18 @@
           <t>2026-02-06 17:05</t>
         </is>
       </c>
-      <c r="M137" t="inlineStr"/>
       <c r="N137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0</v>
+      </c>
+      <c r="R137" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T137" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75129,8 +75349,18 @@
           <t>2026-02-06 17:05</t>
         </is>
       </c>
-      <c r="M138" t="inlineStr"/>
       <c r="N138" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0</v>
+      </c>
+      <c r="R138" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T138" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75185,8 +75415,18 @@
           <t>2026-02-08 12:52</t>
         </is>
       </c>
-      <c r="M139" t="inlineStr"/>
       <c r="N139" t="n">
+        <v>0</v>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q139" t="n">
+        <v>0</v>
+      </c>
+      <c r="T139" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75231,8 +75471,18 @@
           <t>2026-02-07 14:28</t>
         </is>
       </c>
-      <c r="M140" t="inlineStr"/>
       <c r="N140" t="n">
+        <v>0</v>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q140" t="n">
+        <v>0</v>
+      </c>
+      <c r="T140" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75277,8 +75527,18 @@
           <t>2026-02-08 16:39</t>
         </is>
       </c>
-      <c r="M141" t="inlineStr"/>
       <c r="N141" t="n">
+        <v>0</v>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q141" t="n">
+        <v>0</v>
+      </c>
+      <c r="T141" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75333,8 +75593,18 @@
           <t>2026-02-07 16:52</t>
         </is>
       </c>
-      <c r="M142" t="inlineStr"/>
       <c r="N142" t="n">
+        <v>0</v>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>0</v>
+      </c>
+      <c r="T142" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75389,8 +75659,18 @@
           <t>2026-02-07 16:08</t>
         </is>
       </c>
-      <c r="M143" t="inlineStr"/>
       <c r="N143" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0</v>
+      </c>
+      <c r="R143" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T143" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75445,8 +75725,18 @@
           <t>2026-02-08 14:22</t>
         </is>
       </c>
-      <c r="M144" t="inlineStr"/>
       <c r="N144" t="n">
+        <v>0</v>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>0</v>
+      </c>
+      <c r="T144" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75491,8 +75781,18 @@
           <t>2026-02-08 14:21</t>
         </is>
       </c>
-      <c r="M145" t="inlineStr"/>
       <c r="N145" t="n">
+        <v>0</v>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>0</v>
+      </c>
+      <c r="T145" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75547,8 +75847,18 @@
           <t>2026-02-08 14:21</t>
         </is>
       </c>
-      <c r="M146" t="inlineStr"/>
       <c r="N146" t="n">
+        <v>0</v>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>0</v>
+      </c>
+      <c r="T146" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75603,8 +75913,18 @@
           <t>2026-02-14 08:12</t>
         </is>
       </c>
-      <c r="M147" t="inlineStr"/>
       <c r="N147" t="n">
+        <v>0</v>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>0</v>
+      </c>
+      <c r="T147" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75649,8 +75969,18 @@
           <t>2026-02-14 08:12</t>
         </is>
       </c>
-      <c r="M148" t="inlineStr"/>
       <c r="N148" t="n">
+        <v>0</v>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>0</v>
+      </c>
+      <c r="T148" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75705,8 +76035,18 @@
           <t>2026-02-13 11:32</t>
         </is>
       </c>
-      <c r="M149" t="inlineStr"/>
       <c r="N149" t="n">
+        <v>0</v>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q149" t="n">
+        <v>0</v>
+      </c>
+      <c r="T149" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75751,8 +76091,18 @@
           <t>2026-02-12 08:51</t>
         </is>
       </c>
-      <c r="M150" t="inlineStr"/>
       <c r="N150" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q150" t="n">
+        <v>0</v>
+      </c>
+      <c r="R150" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T150" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75797,8 +76147,13 @@
           <t>2026-02-12 22:31</t>
         </is>
       </c>
-      <c r="M151" t="inlineStr"/>
       <c r="N151" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q151" t="n">
+        <v>0</v>
+      </c>
+      <c r="T151" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75843,8 +76198,18 @@
           <t>2026-02-13 21:55</t>
         </is>
       </c>
-      <c r="M152" t="inlineStr"/>
       <c r="N152" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q152" t="n">
+        <v>0</v>
+      </c>
+      <c r="R152" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T152" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75889,8 +76254,18 @@
           <t>2026-02-15 16:48</t>
         </is>
       </c>
-      <c r="M153" t="inlineStr"/>
       <c r="N153" t="n">
+        <v>0</v>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q153" t="n">
+        <v>0</v>
+      </c>
+      <c r="T153" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75935,8 +76310,18 @@
           <t>2026-02-15 16:48</t>
         </is>
       </c>
-      <c r="M154" t="inlineStr"/>
       <c r="N154" t="n">
+        <v>0</v>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q154" t="n">
+        <v>0</v>
+      </c>
+      <c r="T154" t="n">
         <v>0</v>
       </c>
     </row>
@@ -75981,8 +76366,18 @@
           <t>2026-02-14 19:56</t>
         </is>
       </c>
-      <c r="M155" t="inlineStr"/>
       <c r="N155" t="n">
+        <v>0</v>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q155" t="n">
+        <v>0</v>
+      </c>
+      <c r="T155" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76027,8 +76422,18 @@
           <t>2026-02-14 16:43</t>
         </is>
       </c>
-      <c r="M156" t="inlineStr"/>
       <c r="N156" t="n">
+        <v>0</v>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q156" t="n">
+        <v>0</v>
+      </c>
+      <c r="T156" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76073,8 +76478,18 @@
           <t>2026-02-20 16:26</t>
         </is>
       </c>
-      <c r="M157" t="inlineStr"/>
       <c r="N157" t="n">
+        <v>0</v>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q157" t="n">
+        <v>0</v>
+      </c>
+      <c r="T157" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76129,8 +76544,18 @@
           <t>2026-02-16 09:54</t>
         </is>
       </c>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="n">
+        <v>0</v>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q158" t="n">
+        <v>0</v>
+      </c>
+      <c r="T158" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76175,8 +76600,18 @@
           <t>2026-02-17 15:59</t>
         </is>
       </c>
-      <c r="M159" t="inlineStr"/>
       <c r="N159" t="n">
+        <v>0</v>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q159" t="n">
+        <v>0</v>
+      </c>
+      <c r="T159" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76221,8 +76656,18 @@
           <t>2026-02-17 21:35</t>
         </is>
       </c>
-      <c r="M160" t="inlineStr"/>
       <c r="N160" t="n">
+        <v>0</v>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q160" t="n">
+        <v>0</v>
+      </c>
+      <c r="T160" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76277,8 +76722,18 @@
           <t>2026-02-20 09:24</t>
         </is>
       </c>
-      <c r="M161" t="inlineStr"/>
       <c r="N161" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q161" t="n">
+        <v>0</v>
+      </c>
+      <c r="R161" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T161" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76323,8 +76778,18 @@
           <t>2026-02-20 17:28</t>
         </is>
       </c>
-      <c r="M162" t="inlineStr"/>
       <c r="N162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
+        <v>0</v>
+      </c>
+      <c r="R162" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T162" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76369,8 +76834,18 @@
           <t>2026-02-22 16:45</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr"/>
       <c r="N163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q163" t="n">
+        <v>0</v>
+      </c>
+      <c r="T163" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76415,8 +76890,18 @@
           <t>2026-02-22 16:45</t>
         </is>
       </c>
-      <c r="M164" t="inlineStr"/>
       <c r="N164" t="n">
+        <v>0</v>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q164" t="n">
+        <v>0</v>
+      </c>
+      <c r="T164" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76461,8 +76946,18 @@
           <t>2026-02-22 16:26</t>
         </is>
       </c>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q165" t="n">
+        <v>0</v>
+      </c>
+      <c r="R165" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T165" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76507,8 +77002,18 @@
           <t>2026-02-21 16:31</t>
         </is>
       </c>
-      <c r="M166" t="inlineStr"/>
       <c r="N166" t="n">
+        <v>0</v>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q166" t="n">
+        <v>0</v>
+      </c>
+      <c r="T166" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76553,8 +77058,18 @@
           <t>2026-02-22 13:21</t>
         </is>
       </c>
-      <c r="M167" t="inlineStr"/>
       <c r="N167" t="n">
+        <v>0</v>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>0</v>
+      </c>
+      <c r="T167" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76599,8 +77114,18 @@
           <t>2026-02-21 15:43</t>
         </is>
       </c>
-      <c r="M168" t="inlineStr"/>
       <c r="N168" t="n">
+        <v>0</v>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>0</v>
+      </c>
+      <c r="T168" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76645,8 +77170,18 @@
           <t>2026-02-22 14:15</t>
         </is>
       </c>
-      <c r="M169" t="inlineStr"/>
       <c r="N169" t="n">
+        <v>0</v>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>0</v>
+      </c>
+      <c r="T169" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76691,8 +77226,18 @@
           <t>2026-02-22 14:15</t>
         </is>
       </c>
-      <c r="M170" t="inlineStr"/>
       <c r="N170" t="n">
+        <v>0</v>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>0</v>
+      </c>
+      <c r="T170" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76737,8 +77282,18 @@
           <t>2026-02-24 14:39</t>
         </is>
       </c>
-      <c r="M171" t="inlineStr"/>
       <c r="N171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76783,8 +77338,18 @@
           <t>2026-02-25 11:05</t>
         </is>
       </c>
-      <c r="M172" t="inlineStr"/>
       <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>0</v>
+      </c>
+      <c r="T172" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76829,8 +77394,18 @@
           <t>2026-02-24 16:31</t>
         </is>
       </c>
-      <c r="M173" t="inlineStr"/>
       <c r="N173" t="n">
+        <v>0</v>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>0</v>
+      </c>
+      <c r="T173" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76875,8 +77450,18 @@
           <t>2026-02-24 14:14</t>
         </is>
       </c>
-      <c r="M174" t="inlineStr"/>
       <c r="N174" t="n">
+        <v>0</v>
+      </c>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>0</v>
+      </c>
+      <c r="T174" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76921,8 +77506,18 @@
           <t>2026-02-25 08:29</t>
         </is>
       </c>
-      <c r="M175" t="inlineStr"/>
       <c r="N175" t="n">
+        <v>0</v>
+      </c>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>0</v>
+      </c>
+      <c r="T175" t="n">
         <v>0</v>
       </c>
     </row>
@@ -76977,8 +77572,18 @@
           <t>2026-02-26 15:06</t>
         </is>
       </c>
-      <c r="M176" t="inlineStr"/>
       <c r="N176" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q176" t="n">
+        <v>0</v>
+      </c>
+      <c r="R176" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T176" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77023,8 +77628,18 @@
           <t>2026-02-28 13:00</t>
         </is>
       </c>
-      <c r="M177" t="inlineStr"/>
       <c r="N177" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q177" t="n">
+        <v>0</v>
+      </c>
+      <c r="R177" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T177" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77069,8 +77684,18 @@
           <t>2026-03-01 09:59</t>
         </is>
       </c>
-      <c r="M178" t="inlineStr"/>
       <c r="N178" t="n">
+        <v>0</v>
+      </c>
+      <c r="P178" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q178" t="n">
+        <v>0</v>
+      </c>
+      <c r="T178" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77125,8 +77750,18 @@
           <t>2026-03-02 08:32</t>
         </is>
       </c>
-      <c r="M179" t="inlineStr"/>
       <c r="N179" t="n">
+        <v>0</v>
+      </c>
+      <c r="P179" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q179" t="n">
+        <v>0</v>
+      </c>
+      <c r="T179" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77171,8 +77806,18 @@
           <t>2026-03-05 16:02</t>
         </is>
       </c>
-      <c r="M180" t="inlineStr"/>
       <c r="N180" t="n">
+        <v>0</v>
+      </c>
+      <c r="P180" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q180" t="n">
+        <v>0</v>
+      </c>
+      <c r="T180" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77217,8 +77862,18 @@
           <t>2026-03-08 11:54</t>
         </is>
       </c>
-      <c r="M181" t="inlineStr"/>
       <c r="N181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q181" t="n">
+        <v>0</v>
+      </c>
+      <c r="T181" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77263,8 +77918,18 @@
           <t>2026-03-07 16:12</t>
         </is>
       </c>
-      <c r="M182" t="inlineStr"/>
       <c r="N182" t="n">
+        <v>0</v>
+      </c>
+      <c r="P182" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q182" t="n">
+        <v>0</v>
+      </c>
+      <c r="T182" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77319,8 +77984,18 @@
           <t>2026-03-08 12:29</t>
         </is>
       </c>
-      <c r="M183" t="inlineStr"/>
       <c r="N183" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q183" t="n">
+        <v>0</v>
+      </c>
+      <c r="R183" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T183" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77365,8 +78040,18 @@
           <t>2026-03-08 12:12</t>
         </is>
       </c>
-      <c r="M184" t="inlineStr"/>
       <c r="N184" t="n">
+        <v>0</v>
+      </c>
+      <c r="P184" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q184" t="n">
+        <v>0</v>
+      </c>
+      <c r="T184" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77411,8 +78096,18 @@
           <t>2026-03-08 12:12</t>
         </is>
       </c>
-      <c r="M185" t="inlineStr"/>
       <c r="N185" t="n">
+        <v>0</v>
+      </c>
+      <c r="P185" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q185" t="n">
+        <v>0</v>
+      </c>
+      <c r="T185" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77457,8 +78152,18 @@
           <t>2026-03-08 13:26</t>
         </is>
       </c>
-      <c r="M186" t="inlineStr"/>
       <c r="N186" t="n">
+        <v>0</v>
+      </c>
+      <c r="P186" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q186" t="n">
+        <v>0</v>
+      </c>
+      <c r="T186" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77503,8 +78208,18 @@
           <t>2026-03-08 07:55</t>
         </is>
       </c>
-      <c r="M187" t="inlineStr"/>
       <c r="N187" t="n">
+        <v>0</v>
+      </c>
+      <c r="P187" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q187" t="n">
+        <v>0</v>
+      </c>
+      <c r="T187" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77549,8 +78264,18 @@
           <t>2026-03-08 11:03</t>
         </is>
       </c>
-      <c r="M188" t="inlineStr"/>
       <c r="N188" t="n">
+        <v>0</v>
+      </c>
+      <c r="P188" t="inlineStr">
+        <is>
+          <t>体验</t>
+        </is>
+      </c>
+      <c r="Q188" t="n">
+        <v>0</v>
+      </c>
+      <c r="T188" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77585,8 +78310,13 @@
           <t>2026-03-08 11:16</t>
         </is>
       </c>
-      <c r="M189" t="inlineStr"/>
       <c r="N189" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q189" t="n">
+        <v>0</v>
+      </c>
+      <c r="T189" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77631,8 +78361,18 @@
           <t>2026-03-10 12:44</t>
         </is>
       </c>
-      <c r="M190" t="inlineStr"/>
       <c r="N190" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q190" t="n">
+        <v>0</v>
+      </c>
+      <c r="R190" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T190" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77687,8 +78427,18 @@
           <t>2026-03-10 12:44</t>
         </is>
       </c>
-      <c r="M191" t="inlineStr"/>
       <c r="N191" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q191" t="n">
+        <v>0</v>
+      </c>
+      <c r="R191" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T191" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77743,8 +78493,18 @@
           <t>2026-03-13 12:38</t>
         </is>
       </c>
-      <c r="M192" t="inlineStr"/>
       <c r="N192" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q192" t="n">
+        <v>0</v>
+      </c>
+      <c r="R192" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T192" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77799,8 +78559,18 @@
           <t>2026-03-14 15:11</t>
         </is>
       </c>
-      <c r="M193" t="inlineStr"/>
       <c r="N193" t="n">
+        <v>0</v>
+      </c>
+      <c r="O193" t="inlineStr">
+        <is>
+          <t>招待</t>
+        </is>
+      </c>
+      <c r="Q193" t="n">
+        <v>0</v>
+      </c>
+      <c r="T193" t="n">
         <v>0</v>
       </c>
     </row>
@@ -77855,9 +78625,14 @@
           <t>2026-03-16 13:32</t>
         </is>
       </c>
-      <c r="M194" t="inlineStr"/>
       <c r="N194" t="n">
         <v>0</v>
+      </c>
+      <c r="Q194" t="n">
+        <v>0</v>
+      </c>
+      <c r="T194" t="n">
+        <v>220</v>
       </c>
     </row>
     <row r="195">
@@ -77891,8 +78666,18 @@
           <t>2026-03-22 11:19</t>
         </is>
       </c>
-      <c r="M195" t="inlineStr"/>
       <c r="N195" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q195" t="n">
+        <v>0</v>
+      </c>
+      <c r="R195" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="T195" t="n">
         <v>0</v>
       </c>
     </row>
